--- a/9. PCM - Previsão de Gastos 2025 e 2026.xlsx
+++ b/9. PCM - Previsão de Gastos 2025 e 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\_files\projecao_gastos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{69B6720E-54A2-4D4F-B869-41DB6BF32AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F330B7EB-1633-462D-81C1-53262A7C22DF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623D6F55-3CA4-41D7-8896-C57074F1BF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="714" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="153">
   <si>
     <t>Status</t>
   </si>
@@ -202,46 +202,18 @@
 CONTÁBIL</t>
   </si>
   <si>
-    <t>NÚMERO DA 
-NOTA FISCAL</t>
-  </si>
-  <si>
-    <t>TIPO DE 
-SOLICITAÇÃO</t>
-  </si>
-  <si>
     <t>ORDEM 
 DE SERVIÇO</t>
-  </si>
-  <si>
-    <t>DATA DE ABERTURA 
-DA REQUISIÇÃO</t>
   </si>
   <si>
     <t>FORNECEDOR
 CNPJ</t>
   </si>
   <si>
-    <t>NÚEMRO DA REQUISIÇÃO 
-DE COMPRA</t>
-  </si>
-  <si>
-    <t>NÚMERO DO 
-PEDIDO DE COMPRA</t>
-  </si>
-  <si>
-    <t>NF DE SERVIÇO
- RECEBIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NF ENVIADA
- PARA LANÇAMENTO </t>
-  </si>
-  <si>
     <t>OBSERVAÇÕES</t>
   </si>
   <si>
-    <t>CLEITON</t>
+    <t>CLEITON-DESTRI</t>
   </si>
   <si>
     <t>MULT-TEC</t>
@@ -268,7 +240,7 @@
     <t xml:space="preserve">SERVIÇO PARA RECUPERAR CAIXA DE SELAGEM DA PRESUNTARIA </t>
   </si>
   <si>
-    <t>RHUAN</t>
+    <t>RHUAN-GIMENES</t>
   </si>
   <si>
     <t>USICASTRO (PHDS)</t>
@@ -292,7 +264,7 @@
     <t>novembro 2025</t>
   </si>
   <si>
-    <t>JOSÉ</t>
+    <t>JOSE-ADENILSON</t>
   </si>
   <si>
     <t>PESO EXATO</t>
@@ -370,9 +342,6 @@
     <t>SERVIÇO DE MATERIAL E MÃO DE OBRA PARA REVISÃO PREVENTIVA DA CENTRIFUGA TRIDECANTER DCT SATURNO 3 (N° 3019)</t>
   </si>
   <si>
-    <t xml:space="preserve">CLEITON </t>
-  </si>
-  <si>
     <t>MULTIVAC</t>
   </si>
   <si>
@@ -445,6 +414,9 @@
     </r>
   </si>
   <si>
+    <t>Não aprovado prosseguir com orçamento prévio, necessário orçamento definitivo para abertura da Requisição.</t>
+  </si>
+  <si>
     <t>SERVIÇO TERCEIRO: MATERIAL E MÃO DE OBRA PARA REVISÃO DO EQUIPAMENTO SERRA AUTOMÁTICA SPLITTER MSP6040</t>
   </si>
   <si>
@@ -469,10 +441,40 @@
     <t>SERVIÇO DE CONSERTO EM MODULO CONTROLADOR INSENSIBILIZADOR DE CHOQUE MANUAL</t>
   </si>
   <si>
+    <t>SERV EXTERNO</t>
+  </si>
+  <si>
     <t>AUTRON</t>
   </si>
   <si>
-    <t>SERVIÇO DE CONSERTO EM SERVOMOTOR DE ACIONAMENTO PORTA V-CUT</t>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SERVIÇO DE CONSERTO EM SERVOMOTOR DE ACIONAMENTO PORTA V-CUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SOLICITADO DEVOLUÇÃO DEVIDO ALTO VALOR</t>
+    </r>
   </si>
   <si>
     <t>FPN - CONTROLE E AUTOMACAO INDUSTRIAL</t>
@@ -504,7 +506,7 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>PEDIDO DEVOLUÇÃO DEVIDO ALTO VALOR</t>
+      <t>SOLICITADO DEVOLUÇÃO DEVIDO ALTO VALOR</t>
     </r>
   </si>
   <si>
@@ -521,9 +523,6 @@
   </si>
   <si>
     <t>REVISÃO PREVENTIVA PRENSA EXPELLER 3000 FFG - MATERIAL + MÃO DE OBRA</t>
-  </si>
-  <si>
-    <t>JOSE-ADENILSON</t>
   </si>
   <si>
     <t xml:space="preserve">MAREL </t>
@@ -567,17 +566,32 @@
   <si>
     <t xml:space="preserve">MANUTENÇÃO EM BORRACHAS DO DEPILADOR CONTÍNUO (TROCA DE TODAS AS BORRACHAS) </t>
   </si>
+  <si>
+    <t>NÚMERO DO PEDIDO DE COMPRA</t>
+  </si>
+  <si>
+    <t>NÚEMRO DA REQUISIÇÃO DE COMPRA</t>
+  </si>
+  <si>
+    <t>DATA DE ABERTURA DA REQUISIÇÃO</t>
+  </si>
+  <si>
+    <t>NÚMERO DA NOTA FISCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TESTE </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="[$R$-416]\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$R$-416]\ #,##0.00"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -697,6 +711,11 @@
       <strike/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -867,10 +886,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -921,7 +940,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -933,7 +952,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -949,7 +968,7 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -969,7 +988,7 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -982,7 +1001,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1005,7 +1024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1017,7 +1036,7 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1036,7 +1055,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1079,16 +1098,13 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1118,10 +1134,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1133,9 +1146,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1145,16 +1155,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="normal 2" xfId="2" xr:uid="{5F3565CC-B7E1-4600-8CE0-2FF16F9B60ED}"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1185,7 +1211,41 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="[$R$-416]\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -1236,34 +1296,7 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <numFmt numFmtId="165" formatCode="[$R$-416]\ #,##0.00"/>
     </dxf>
     <dxf>
       <fill>
@@ -1294,18 +1327,7 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1323,7 +1345,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1575,7 +1597,7 @@
                   <c:v>MARÇO / 2026</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>(blank)</c:v>
+                  <c:v>(vazio)</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>SEM PREVISÃO</c:v>
@@ -12109,7 +12131,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5662E1A-D9A7-4B7F-87EB-71919FB939AC}" name="Tabela dinâmica1" cacheId="714" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5662E1A-D9A7-4B7F-87EB-71919FB939AC}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="C3:D12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -12192,25 +12214,25 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Soma de VALOR TOTAL" fld="4" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="Soma de VALOR TOTAL" fld="4" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="0">
+    <format dxfId="17">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="14">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="12">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12219,7 +12241,20 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="11">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="7">
@@ -12229,42 +12264,29 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="5">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="3">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="16">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="17">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -12609,7 +12631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18609D9C-E791-48E2-AC72-7D0345E1E97F}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="3" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" style="3" customWidth="1"/>
@@ -12622,7 +12644,7 @@
     <col min="9" max="9" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="7" customFormat="1" ht="28.5">
+    <row r="1" spans="1:9" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -12649,7 +12671,7 @@
       </c>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>8</v>
@@ -12673,7 +12695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -12697,7 +12719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -12721,7 +12743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>19</v>
@@ -12737,7 +12759,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>21</v>
@@ -12751,7 +12773,7 @@
       <c r="G6" s="10"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>23</v>
@@ -12765,7 +12787,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>25</v>
@@ -12779,7 +12801,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -12793,7 +12815,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>29</v>
@@ -12807,7 +12829,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -12821,7 +12843,7 @@
       <c r="G11" s="10"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -12833,7 +12855,7 @@
       <c r="G12" s="10"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -12845,7 +12867,7 @@
       <c r="G13" s="10"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -12857,7 +12879,7 @@
       <c r="G14" s="10"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -12869,13 +12891,13 @@
       <c r="G15" s="10"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="4:4">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" s="4" t="s">
         <v>38</v>
       </c>
@@ -12890,7 +12912,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4816FC4B-CBAA-4EA2-9E15-76188666193F}">
   <dimension ref="A1:AL48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="8" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="8" customWidth="1"/>
@@ -12901,7 +12923,7 @@
     <col min="8" max="38" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="32"/>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -12938,7 +12960,7 @@
       <c r="AH1" s="32"/>
       <c r="AI1" s="32"/>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="32"/>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -12975,7 +12997,7 @@
       <c r="AH2" s="32"/>
       <c r="AI2" s="32"/>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="32"/>
       <c r="B3" s="33"/>
       <c r="C3" t="s">
@@ -13016,13 +13038,13 @@
       <c r="AH3" s="32"/>
       <c r="AI3" s="32"/>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="32"/>
       <c r="B4" s="33"/>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="85">
+      <c r="D4" s="82">
         <v>0</v>
       </c>
       <c r="E4" s="34"/>
@@ -13057,13 +13079,13 @@
       <c r="AH4" s="32"/>
       <c r="AI4" s="32"/>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="32"/>
       <c r="B5" s="33"/>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="82">
         <v>38804.79</v>
       </c>
       <c r="E5" s="34"/>
@@ -13098,13 +13120,13 @@
       <c r="AH5" s="32"/>
       <c r="AI5" s="32"/>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="32"/>
       <c r="B6" s="33"/>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="82">
         <v>483172.23000000004</v>
       </c>
       <c r="E6" s="34"/>
@@ -13139,13 +13161,13 @@
       <c r="AH6" s="32"/>
       <c r="AI6" s="32"/>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="32"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="82">
         <v>0</v>
       </c>
       <c r="E7" s="34"/>
@@ -13180,13 +13202,13 @@
       <c r="AH7" s="32"/>
       <c r="AI7" s="32"/>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="32"/>
       <c r="B8" s="33"/>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="82">
         <v>391442.98000000004</v>
       </c>
       <c r="E8" s="34"/>
@@ -13221,13 +13243,13 @@
       <c r="AH8" s="32"/>
       <c r="AI8" s="32"/>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
       <c r="B9" s="33"/>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="85"/>
+      <c r="D9" s="82"/>
       <c r="E9" s="34"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -13260,13 +13282,13 @@
       <c r="AH9" s="32"/>
       <c r="AI9" s="32"/>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="32"/>
       <c r="B10" s="33"/>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="85">
+      <c r="D10" s="82">
         <v>257814.19</v>
       </c>
       <c r="E10" s="34"/>
@@ -13301,13 +13323,13 @@
       <c r="AH10" s="32"/>
       <c r="AI10" s="32"/>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="32"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="85">
+      <c r="D11" s="82">
         <v>0</v>
       </c>
       <c r="E11" s="34"/>
@@ -13342,13 +13364,13 @@
       <c r="AH11" s="32"/>
       <c r="AI11" s="32"/>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="32"/>
       <c r="B12" s="33"/>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="85">
+      <c r="D12" s="82">
         <v>1171234.19</v>
       </c>
       <c r="E12" s="34"/>
@@ -13383,7 +13405,7 @@
       <c r="AH12" s="32"/>
       <c r="AI12" s="32"/>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="32"/>
       <c r="B13" s="33"/>
       <c r="C13"/>
@@ -13420,7 +13442,7 @@
       <c r="AH13" s="32"/>
       <c r="AI13" s="32"/>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="32"/>
       <c r="B14" s="33"/>
       <c r="C14"/>
@@ -13457,7 +13479,7 @@
       <c r="AH14" s="32"/>
       <c r="AI14" s="32"/>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="32"/>
       <c r="B15" s="33"/>
       <c r="C15"/>
@@ -13494,7 +13516,7 @@
       <c r="AH15" s="32"/>
       <c r="AI15" s="32"/>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="33"/>
       <c r="C16"/>
@@ -13531,7 +13553,7 @@
       <c r="AH16" s="32"/>
       <c r="AI16" s="32"/>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="32"/>
       <c r="B17" s="33"/>
       <c r="C17"/>
@@ -13568,7 +13590,7 @@
       <c r="AH17" s="32"/>
       <c r="AI17" s="32"/>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="32"/>
       <c r="B18" s="33"/>
       <c r="C18"/>
@@ -13605,7 +13627,7 @@
       <c r="AH18" s="32"/>
       <c r="AI18" s="32"/>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="32"/>
       <c r="B19" s="33"/>
       <c r="C19"/>
@@ -13642,7 +13664,7 @@
       <c r="AH19" s="32"/>
       <c r="AI19" s="32"/>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="32"/>
       <c r="B20" s="33"/>
       <c r="C20"/>
@@ -13679,7 +13701,7 @@
       <c r="AH20" s="32"/>
       <c r="AI20" s="32"/>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
       <c r="B21" s="33"/>
       <c r="C21"/>
@@ -13716,7 +13738,7 @@
       <c r="AH21" s="32"/>
       <c r="AI21" s="32"/>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="32"/>
       <c r="B22" s="33"/>
       <c r="C22"/>
@@ -13753,7 +13775,7 @@
       <c r="AH22" s="32"/>
       <c r="AI22" s="32"/>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="32"/>
       <c r="B23" s="33"/>
       <c r="C23"/>
@@ -13790,7 +13812,7 @@
       <c r="AH23" s="32"/>
       <c r="AI23" s="32"/>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="32"/>
       <c r="B24" s="33"/>
       <c r="C24"/>
@@ -13827,7 +13849,7 @@
       <c r="AH24" s="32"/>
       <c r="AI24" s="32"/>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="32"/>
       <c r="B25" s="33"/>
       <c r="C25"/>
@@ -13864,7 +13886,7 @@
       <c r="AH25" s="32"/>
       <c r="AI25" s="32"/>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="32"/>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
@@ -13901,7 +13923,7 @@
       <c r="AH26" s="32"/>
       <c r="AI26" s="32"/>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="32"/>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
@@ -13938,7 +13960,7 @@
       <c r="AH27" s="32"/>
       <c r="AI27" s="32"/>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="32"/>
       <c r="B28" s="32"/>
       <c r="C28" s="32"/>
@@ -13975,7 +13997,7 @@
       <c r="AH28" s="32"/>
       <c r="AI28" s="32"/>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="32"/>
       <c r="B29" s="32"/>
       <c r="C29" s="32"/>
@@ -14012,7 +14034,7 @@
       <c r="AH29" s="32"/>
       <c r="AI29" s="32"/>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="32"/>
       <c r="B30" s="32"/>
       <c r="C30" s="32"/>
@@ -14049,7 +14071,7 @@
       <c r="AH30" s="32"/>
       <c r="AI30" s="32"/>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="32"/>
       <c r="B31" s="32"/>
       <c r="C31" s="32"/>
@@ -14086,7 +14108,7 @@
       <c r="AH31" s="32"/>
       <c r="AI31" s="32"/>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="32"/>
       <c r="B32" s="32"/>
       <c r="C32" s="32"/>
@@ -14123,7 +14145,7 @@
       <c r="AH32" s="32"/>
       <c r="AI32" s="32"/>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
       <c r="B33" s="32"/>
       <c r="C33" s="32"/>
@@ -14160,7 +14182,7 @@
       <c r="AH33" s="32"/>
       <c r="AI33" s="32"/>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" s="32"/>
       <c r="B34" s="32"/>
       <c r="C34" s="32"/>
@@ -14197,7 +14219,7 @@
       <c r="AH34" s="32"/>
       <c r="AI34" s="32"/>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" s="32"/>
       <c r="B35" s="32"/>
       <c r="C35" s="32"/>
@@ -14234,7 +14256,7 @@
       <c r="AH35" s="32"/>
       <c r="AI35" s="32"/>
     </row>
-    <row r="36" spans="1:35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" s="32"/>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -14271,7 +14293,7 @@
       <c r="AH36" s="32"/>
       <c r="AI36" s="32"/>
     </row>
-    <row r="37" spans="1:35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
@@ -14308,7 +14330,7 @@
       <c r="AH37" s="32"/>
       <c r="AI37" s="32"/>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="32"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -14345,7 +14367,7 @@
       <c r="AH38" s="32"/>
       <c r="AI38" s="32"/>
     </row>
-    <row r="39" spans="1:35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
       <c r="B39" s="32"/>
       <c r="C39" s="32"/>
@@ -14382,7 +14404,7 @@
       <c r="AH39" s="32"/>
       <c r="AI39" s="32"/>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="32"/>
       <c r="B40" s="32"/>
       <c r="C40" s="32"/>
@@ -14419,7 +14441,7 @@
       <c r="AH40" s="32"/>
       <c r="AI40" s="32"/>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" s="32"/>
       <c r="B41" s="32"/>
       <c r="C41" s="32"/>
@@ -14456,7 +14478,7 @@
       <c r="AH41" s="32"/>
       <c r="AI41" s="32"/>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="32"/>
       <c r="B42" s="32"/>
       <c r="C42" s="32"/>
@@ -14493,7 +14515,7 @@
       <c r="AH42" s="32"/>
       <c r="AI42" s="32"/>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" s="32"/>
       <c r="B43" s="32"/>
       <c r="C43" s="32"/>
@@ -14530,7 +14552,7 @@
       <c r="AH43" s="32"/>
       <c r="AI43" s="32"/>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
       <c r="B44" s="32"/>
       <c r="C44" s="32"/>
@@ -14567,7 +14589,7 @@
       <c r="AH44" s="32"/>
       <c r="AI44" s="32"/>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" s="32"/>
       <c r="B45" s="32"/>
       <c r="C45" s="32"/>
@@ -14604,7 +14626,7 @@
       <c r="AH45" s="32"/>
       <c r="AI45" s="32"/>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="32"/>
       <c r="B46" s="32"/>
       <c r="C46" s="32"/>
@@ -14641,7 +14663,7 @@
       <c r="AH46" s="32"/>
       <c r="AI46" s="32"/>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="32"/>
       <c r="B47" s="32"/>
       <c r="C47" s="32"/>
@@ -14678,7 +14700,7 @@
       <c r="AH47" s="32"/>
       <c r="AI47" s="32"/>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="32"/>
       <c r="B48" s="32"/>
       <c r="C48" s="32"/>
@@ -14724,7 +14746,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76ED07C-DAA3-4D41-A63E-9156D961F4A2}">
   <dimension ref="A1:S501"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" style="26" customWidth="1"/>
@@ -14747,7 +14769,7 @@
     <col min="20" max="16384" width="9.140625" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="35" customFormat="1" ht="52.5" customHeight="1">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
         <v>44</v>
       </c>
@@ -14773,40 +14795,40 @@
         <v>50</v>
       </c>
       <c r="I1" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="L1" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="M1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>55</v>
-      </c>
       <c r="N1" s="12" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="P1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -14814,13 +14836,13 @@
         <v>29</v>
       </c>
       <c r="C2" s="62" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D2" s="54" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="45" t="s">
@@ -14844,20 +14866,20 @@
       <c r="O2" s="60">
         <v>4408524</v>
       </c>
-      <c r="P2" s="64" t="s">
+      <c r="P2" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="64" t="s">
+      <c r="Q2" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="64" t="s">
+      <c r="R2" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="S2" s="64" t="s">
+      <c r="S2" s="63" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -14865,13 +14887,13 @@
         <v>29</v>
       </c>
       <c r="C3" s="62" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D3" s="54" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F3" s="44"/>
       <c r="G3" s="45" t="s">
@@ -14895,34 +14917,34 @@
       <c r="O3" s="60">
         <v>4399765</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="63" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="63" t="s">
-        <v>61</v>
+      <c r="C4" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="45" t="s">
@@ -14946,34 +14968,34 @@
       <c r="O4" s="61">
         <v>4399761</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="P4" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q4" s="64" t="s">
+      <c r="Q4" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="64" t="s">
+      <c r="R4" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S4" s="64" t="s">
+      <c r="S4" s="63" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30">
+    <row r="5" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="63" t="s">
-        <v>61</v>
+      <c r="C5" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="45" t="s">
@@ -14997,34 +15019,34 @@
       <c r="O5" s="61">
         <v>4390655</v>
       </c>
-      <c r="P5" s="64" t="s">
+      <c r="P5" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="64" t="s">
+      <c r="Q5" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="64" t="s">
+      <c r="R5" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="64" t="s">
+      <c r="S5" s="63" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="63" t="s">
-        <v>61</v>
+      <c r="C6" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="45" t="s">
@@ -15048,34 +15070,34 @@
       <c r="O6" s="61">
         <v>4390653</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q6" s="64" t="s">
+      <c r="Q6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="64" t="s">
+      <c r="R6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S6" s="64" t="s">
+      <c r="S6" s="63" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="56" t="s">
-        <v>68</v>
-      </c>
       <c r="E7" s="57" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="45" t="s">
@@ -15099,20 +15121,20 @@
       <c r="O7" s="61">
         <v>4399466</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="P7" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q7" s="64" t="s">
+      <c r="Q7" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="64" t="s">
+      <c r="R7" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="S7" s="64" t="s">
+      <c r="S7" s="63" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -15120,25 +15142,25 @@
         <v>29</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E8" s="50" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="13"/>
-      <c r="I8" s="64">
+      <c r="I8" s="63">
         <v>404</v>
       </c>
       <c r="J8" s="37"/>
       <c r="K8" s="51" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L8" s="51"/>
       <c r="M8" s="11"/>
@@ -15148,41 +15170,41 @@
       <c r="O8" s="51">
         <v>4417893</v>
       </c>
-      <c r="P8" s="64" t="s">
+      <c r="P8" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="64" t="s">
+      <c r="Q8" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R8" s="64" t="s">
+      <c r="R8" s="63" t="s">
         <v>10</v>
       </c>
       <c r="S8" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="52" t="s">
-        <v>61</v>
+      <c r="C9" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F9" s="41"/>
       <c r="G9" s="45" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="13"/>
-      <c r="I9" s="64">
+      <c r="I9" s="63">
         <v>338</v>
       </c>
       <c r="J9" s="37"/>
@@ -15194,39 +15216,39 @@
       <c r="N9" s="51">
         <v>4296561</v>
       </c>
-      <c r="O9" s="65">
+      <c r="O9" s="64">
         <v>4413697</v>
       </c>
-      <c r="P9" s="64" t="s">
+      <c r="P9" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="64" t="s">
+      <c r="Q9" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R9" s="64" t="s">
-        <v>76</v>
+      <c r="R9" s="63" t="s">
+        <v>69</v>
       </c>
       <c r="S9" s="13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="52" t="s">
-        <v>78</v>
+      <c r="C10" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="66">
+        <v>73</v>
+      </c>
+      <c r="F10" s="65">
         <v>11000</v>
       </c>
       <c r="G10" s="11" t="s">
@@ -15235,7 +15257,7 @@
       <c r="H10" s="13">
         <v>242</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="63" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="37"/>
@@ -15252,18 +15274,18 @@
       <c r="O10" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="64" t="s">
+      <c r="P10" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="64" t="s">
+      <c r="Q10" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="R10" s="64" t="s">
+      <c r="R10" s="63" t="s">
         <v>41</v>
       </c>
       <c r="S10" s="13"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -15271,15 +15293,15 @@
         <v>29</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="66">
+        <v>74</v>
+      </c>
+      <c r="F11" s="65">
         <v>7500</v>
       </c>
       <c r="G11" s="11" t="s">
@@ -15288,7 +15310,7 @@
       <c r="H11" s="13">
         <v>242</v>
       </c>
-      <c r="I11" s="64">
+      <c r="I11" s="63">
         <v>433</v>
       </c>
       <c r="J11" s="37"/>
@@ -15305,18 +15327,18 @@
       <c r="O11" s="51">
         <v>4350050</v>
       </c>
-      <c r="P11" s="64" t="s">
+      <c r="P11" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q11" s="64" t="s">
+      <c r="Q11" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R11" s="64" t="s">
+      <c r="R11" s="63" t="s">
         <v>10</v>
       </c>
       <c r="S11" s="13"/>
     </row>
-    <row r="12" spans="1:19" ht="30">
+    <row r="12" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -15324,15 +15346,15 @@
         <v>29</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E12" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="66">
+        <v>76</v>
+      </c>
+      <c r="F12" s="65">
         <v>3480</v>
       </c>
       <c r="G12" s="11" t="s">
@@ -15341,7 +15363,7 @@
       <c r="H12" s="13">
         <v>242</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="63" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="37"/>
@@ -15358,18 +15380,18 @@
       <c r="O12" s="51">
         <v>4416482</v>
       </c>
-      <c r="P12" s="64" t="s">
+      <c r="P12" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="Q12" s="64" t="s">
+      <c r="Q12" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="R12" s="64" t="s">
+      <c r="R12" s="63" t="s">
         <v>41</v>
       </c>
       <c r="S12" s="13"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -15377,15 +15399,15 @@
         <v>29</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="66">
+        <v>78</v>
+      </c>
+      <c r="F13" s="65">
         <v>3800</v>
       </c>
       <c r="G13" s="11" t="s">
@@ -15394,12 +15416,12 @@
       <c r="H13" s="13">
         <v>242</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="63" t="s">
         <v>41</v>
       </c>
       <c r="J13" s="37"/>
       <c r="K13" s="51" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L13" s="53">
         <v>45973</v>
@@ -15411,18 +15433,18 @@
       <c r="O13" s="51">
         <v>4419988</v>
       </c>
-      <c r="P13" s="64" t="s">
+      <c r="P13" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="Q13" s="64" t="s">
+      <c r="Q13" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="R13" s="64" t="s">
+      <c r="R13" s="63" t="s">
         <v>41</v>
       </c>
       <c r="S13" s="13"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -15430,15 +15452,15 @@
         <v>29</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="66">
+        <v>80</v>
+      </c>
+      <c r="F14" s="65">
         <v>2050</v>
       </c>
       <c r="G14" s="11" t="s">
@@ -15447,12 +15469,12 @@
       <c r="H14" s="13">
         <v>242</v>
       </c>
-      <c r="I14" s="64">
+      <c r="I14" s="63">
         <v>3195</v>
       </c>
       <c r="J14" s="37"/>
       <c r="K14" s="51" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L14" s="53">
         <v>45973</v>
@@ -15464,18 +15486,18 @@
       <c r="O14" s="51">
         <v>4413962</v>
       </c>
-      <c r="P14" s="64" t="s">
+      <c r="P14" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="64" t="s">
+      <c r="Q14" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="64" t="s">
+      <c r="R14" s="63" t="s">
         <v>10</v>
       </c>
       <c r="S14" s="13"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -15483,15 +15505,15 @@
         <v>29</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="F15" s="66">
+        <v>82</v>
+      </c>
+      <c r="F15" s="65">
         <v>765</v>
       </c>
       <c r="G15" s="11" t="s">
@@ -15500,7 +15522,7 @@
       <c r="H15" s="13">
         <v>242</v>
       </c>
-      <c r="I15" s="64">
+      <c r="I15" s="63">
         <v>432</v>
       </c>
       <c r="J15" s="37"/>
@@ -15517,34 +15539,34 @@
       <c r="O15" s="51">
         <v>4424780</v>
       </c>
-      <c r="P15" s="64" t="s">
+      <c r="P15" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="64" t="s">
+      <c r="Q15" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="64" t="s">
+      <c r="R15" s="63" t="s">
         <v>10</v>
       </c>
       <c r="S15" s="13"/>
     </row>
-    <row r="16" spans="1:19" ht="30">
+    <row r="16" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="52" t="s">
-        <v>78</v>
+      <c r="C16" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="66">
+        <v>84</v>
+      </c>
+      <c r="F16" s="65">
         <v>5500</v>
       </c>
       <c r="G16" s="11" t="s">
@@ -15553,7 +15575,7 @@
       <c r="H16" s="13">
         <v>242</v>
       </c>
-      <c r="I16" s="64" t="s">
+      <c r="I16" s="63" t="s">
         <v>41</v>
       </c>
       <c r="J16" s="37"/>
@@ -15570,18 +15592,18 @@
       <c r="O16" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="P16" s="64" t="s">
+      <c r="P16" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="Q16" s="64" t="s">
+      <c r="Q16" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="R16" s="64" t="s">
+      <c r="R16" s="63" t="s">
         <v>41</v>
       </c>
       <c r="S16" s="13"/>
     </row>
-    <row r="17" spans="1:19" ht="45">
+    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -15589,15 +15611,15 @@
         <v>29</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E17" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" s="66">
+        <v>86</v>
+      </c>
+      <c r="F17" s="65">
         <v>4709.79</v>
       </c>
       <c r="G17" s="11" t="s">
@@ -15606,12 +15628,12 @@
       <c r="H17" s="13">
         <v>242</v>
       </c>
-      <c r="I17" s="64" t="s">
+      <c r="I17" s="63" t="s">
         <v>41</v>
       </c>
       <c r="J17" s="37"/>
       <c r="K17" s="51" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L17" s="53">
         <v>46014</v>
@@ -15623,37 +15645,37 @@
       <c r="O17" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="P17" s="64" t="s">
+      <c r="P17" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="Q17" s="64" t="s">
+      <c r="Q17" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="R17" s="64" t="s">
+      <c r="R17" s="63" t="s">
         <v>41</v>
       </c>
       <c r="S17" s="13"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="52" t="s">
-        <v>61</v>
+      <c r="C18" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="66">
+        <v>88</v>
+      </c>
+      <c r="F18" s="65">
         <v>150000</v>
       </c>
-      <c r="G18" s="67" t="s">
+      <c r="G18" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="13">
@@ -15673,7 +15695,7 @@
       <c r="N18" s="51">
         <v>4298167</v>
       </c>
-      <c r="O18" s="68">
+      <c r="O18" s="67">
         <v>4417448</v>
       </c>
       <c r="P18" s="11" t="s">
@@ -15687,7 +15709,7 @@
       </c>
       <c r="S18" s="13"/>
     </row>
-    <row r="19" spans="1:19" ht="30">
+    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -15695,18 +15717,18 @@
         <v>29</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="66">
+        <v>90</v>
+      </c>
+      <c r="F19" s="65">
         <v>20706</v>
       </c>
-      <c r="G19" s="67" t="s">
+      <c r="G19" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H19" s="13">
@@ -15738,7 +15760,7 @@
       </c>
       <c r="S19" s="13"/>
     </row>
-    <row r="20" spans="1:19" ht="30">
+    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -15746,18 +15768,18 @@
         <v>29</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="66">
+        <v>92</v>
+      </c>
+      <c r="F20" s="65">
         <v>406.9</v>
       </c>
-      <c r="G20" s="67" t="s">
+      <c r="G20" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H20" s="13">
@@ -15789,7 +15811,7 @@
       </c>
       <c r="S20" s="13"/>
     </row>
-    <row r="21" spans="1:19" ht="30">
+    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -15797,18 +15819,18 @@
         <v>29</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="66">
+        <v>93</v>
+      </c>
+      <c r="F21" s="65">
         <v>555.12</v>
       </c>
-      <c r="G21" s="67" t="s">
+      <c r="G21" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H21" s="13">
@@ -15824,7 +15846,7 @@
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="51" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O21" s="51">
         <v>4488524</v>
@@ -15840,7 +15862,7 @@
       </c>
       <c r="S21" s="13"/>
     </row>
-    <row r="22" spans="1:19" ht="29.25">
+    <row r="22" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -15848,18 +15870,18 @@
         <v>29</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="66">
+        <v>96</v>
+      </c>
+      <c r="F22" s="65">
         <v>44500</v>
       </c>
-      <c r="G22" s="67" t="s">
+      <c r="G22" s="66" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="13">
@@ -15885,26 +15907,26 @@
       <c r="R22" s="11"/>
       <c r="S22" s="13"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="52" t="s">
-        <v>104</v>
+      <c r="C23" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="F23" s="66">
+        <v>98</v>
+      </c>
+      <c r="F23" s="65">
         <v>6366.24</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H23" s="13">
@@ -15934,26 +15956,26 @@
       </c>
       <c r="S23" s="13"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="52" t="s">
-        <v>104</v>
+      <c r="C24" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="66">
+        <v>100</v>
+      </c>
+      <c r="F24" s="65">
         <v>75000</v>
       </c>
-      <c r="G24" s="67" t="s">
+      <c r="G24" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H24" s="13">
@@ -15961,14 +15983,14 @@
       </c>
       <c r="I24" s="36"/>
       <c r="J24" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="K24" s="74"/>
+        <v>101</v>
+      </c>
+      <c r="K24" s="73"/>
       <c r="L24" s="53">
         <v>191125</v>
       </c>
       <c r="M24" s="11"/>
-      <c r="N24" s="69">
+      <c r="N24" s="68">
         <v>4305416</v>
       </c>
       <c r="O24" s="51"/>
@@ -15983,26 +16005,26 @@
       </c>
       <c r="S24" s="13"/>
     </row>
-    <row r="25" spans="1:19" ht="30">
+    <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="52" t="s">
-        <v>104</v>
+      <c r="C25" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="66">
+        <v>103</v>
+      </c>
+      <c r="F25" s="65">
         <v>12900</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="13">
@@ -16012,17 +16034,17 @@
         <v>2359</v>
       </c>
       <c r="J25" s="37"/>
-      <c r="K25" s="75">
+      <c r="K25" s="74">
         <v>90443</v>
       </c>
-      <c r="L25" s="73">
+      <c r="L25" s="72">
         <v>45968</v>
       </c>
       <c r="M25" s="11"/>
-      <c r="N25" s="70">
+      <c r="N25" s="69">
         <v>4294295</v>
       </c>
-      <c r="O25" s="71"/>
+      <c r="O25" s="70"/>
       <c r="P25" s="11" t="s">
         <v>10</v>
       </c>
@@ -16034,26 +16056,26 @@
       </c>
       <c r="S25" s="13"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="51" t="s">
-        <v>112</v>
-      </c>
       <c r="E26" s="50" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="66">
+        <v>105</v>
+      </c>
+      <c r="F26" s="65">
         <v>21984.21</v>
       </c>
-      <c r="G26" s="67" t="s">
+      <c r="G26" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H26" s="13">
@@ -16061,14 +16083,14 @@
       </c>
       <c r="I26" s="15"/>
       <c r="J26" s="37"/>
-      <c r="K26" s="75">
+      <c r="K26" s="74">
         <v>100069</v>
       </c>
-      <c r="L26" s="73">
+      <c r="L26" s="72">
         <v>46034</v>
       </c>
       <c r="M26" s="11"/>
-      <c r="N26" s="72">
+      <c r="N26" s="71">
         <v>4361017</v>
       </c>
       <c r="O26" s="51"/>
@@ -16083,26 +16105,26 @@
       </c>
       <c r="S26" s="13"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="52" t="s">
-        <v>104</v>
+      <c r="C27" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F27" s="66">
+        <v>107</v>
+      </c>
+      <c r="F27" s="65">
         <v>150000</v>
       </c>
-      <c r="G27" s="67" t="s">
+      <c r="G27" s="66" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="13">
@@ -16128,23 +16150,23 @@
       </c>
       <c r="S27" s="13"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="52" t="s">
-        <v>61</v>
+      <c r="C28" s="62" t="s">
+        <v>54</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" s="66">
+        <v>108</v>
+      </c>
+      <c r="F28" s="65">
         <v>150000</v>
       </c>
       <c r="G28" s="11" t="s">
@@ -16173,23 +16195,23 @@
       <c r="R28" s="11"/>
       <c r="S28" s="13"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="71" t="s">
-        <v>117</v>
+      <c r="C29" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>109</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="F29" s="66">
+        <v>110</v>
+      </c>
+      <c r="F29" s="65">
         <v>120000</v>
       </c>
       <c r="G29" s="11" t="s">
@@ -16218,7 +16240,7 @@
       <c r="R29" s="11"/>
       <c r="S29" s="13"/>
     </row>
-    <row r="30" spans="1:19" ht="30">
+    <row r="30" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -16226,15 +16248,15 @@
         <v>29</v>
       </c>
       <c r="C30" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="66">
+        <v>111</v>
+      </c>
+      <c r="F30" s="65">
         <v>19885</v>
       </c>
       <c r="G30" s="11" t="s">
@@ -16263,23 +16285,23 @@
       <c r="R30" s="11"/>
       <c r="S30" s="13"/>
     </row>
-    <row r="31" spans="1:19" ht="45">
+    <row r="31" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="82" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="78" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" s="76" t="s">
-        <v>121</v>
-      </c>
-      <c r="F31" s="77">
+      <c r="C31" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="76" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="75">
         <v>37363.58</v>
       </c>
       <c r="G31" s="11" t="s">
@@ -16290,25 +16312,27 @@
       </c>
       <c r="I31" s="13"/>
       <c r="J31" s="37"/>
-      <c r="K31" s="78">
+      <c r="K31" s="85">
         <v>100524</v>
       </c>
-      <c r="L31" s="81">
+      <c r="L31" s="86">
         <v>46037</v>
       </c>
       <c r="M31" s="11"/>
-      <c r="N31" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="O31" s="78" t="s">
+      <c r="N31" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="O31" s="76" t="s">
         <v>41</v>
       </c>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
-      <c r="S31" s="16"/>
-    </row>
-    <row r="32" spans="1:19" ht="43.5">
+      <c r="S31" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -16316,15 +16340,15 @@
         <v>29</v>
       </c>
       <c r="C32" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="66">
+        <v>113</v>
+      </c>
+      <c r="F32" s="65">
         <v>64194.400000000001</v>
       </c>
       <c r="G32" s="11" t="s">
@@ -16342,7 +16366,7 @@
         <v>46066</v>
       </c>
       <c r="M32" s="11"/>
-      <c r="N32" s="80">
+      <c r="N32" s="78">
         <v>4391324</v>
       </c>
       <c r="O32" s="51" t="s">
@@ -16353,7 +16377,7 @@
       <c r="R32" s="11"/>
       <c r="S32" s="16"/>
     </row>
-    <row r="33" spans="1:19" ht="30">
+    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -16361,16 +16385,16 @@
         <v>29</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33" s="66" t="s">
-        <v>124</v>
+        <v>116</v>
+      </c>
+      <c r="F33" s="65" t="s">
+        <v>117</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>24</v>
@@ -16388,7 +16412,7 @@
       </c>
       <c r="M33" s="11"/>
       <c r="N33" s="51" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="O33" s="51" t="s">
         <v>41</v>
@@ -16398,7 +16422,7 @@
       <c r="R33" s="11"/>
       <c r="S33" s="16"/>
     </row>
-    <row r="34" spans="1:19" ht="30">
+    <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -16406,16 +16430,16 @@
         <v>29</v>
       </c>
       <c r="C34" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="66" t="s">
-        <v>127</v>
+        <v>119</v>
+      </c>
+      <c r="F34" s="65" t="s">
+        <v>120</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>26</v>
@@ -16426,7 +16450,7 @@
       <c r="I34" s="13"/>
       <c r="J34" s="37"/>
       <c r="K34" s="51" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="L34" s="53">
         <v>46064</v>
@@ -16441,7 +16465,7 @@
       <c r="R34" s="11"/>
       <c r="S34" s="16"/>
     </row>
-    <row r="35" spans="1:19" ht="30">
+    <row r="35" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -16449,15 +16473,15 @@
         <v>29</v>
       </c>
       <c r="C35" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" s="66">
+        <v>123</v>
+      </c>
+      <c r="F35" s="65">
         <v>7030</v>
       </c>
       <c r="G35" s="11" t="s">
@@ -16466,10 +16490,12 @@
       <c r="H35" s="13">
         <v>242</v>
       </c>
-      <c r="I35" s="64">
+      <c r="I35" s="63">
         <v>7104</v>
       </c>
-      <c r="J35" s="37"/>
+      <c r="J35" s="37" t="s">
+        <v>124</v>
+      </c>
       <c r="K35" s="51">
         <v>100105</v>
       </c>
@@ -16494,7 +16520,7 @@
       </c>
       <c r="S35" s="16"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -16502,13 +16528,13 @@
         <v>29</v>
       </c>
       <c r="C36" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" s="50" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="E36" s="83" t="s">
+        <v>126</v>
       </c>
       <c r="F36" s="42">
         <v>0</v>
@@ -16531,7 +16557,7 @@
       <c r="R36" s="11"/>
       <c r="S36" s="16"/>
     </row>
-    <row r="37" spans="1:19" ht="30">
+    <row r="37" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -16539,13 +16565,13 @@
         <v>29</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" s="83" t="s">
-        <v>134</v>
+        <v>127</v>
+      </c>
+      <c r="E37" s="80" t="s">
+        <v>128</v>
       </c>
       <c r="F37" s="42">
         <v>0</v>
@@ -16568,7 +16594,7 @@
       <c r="R37" s="11"/>
       <c r="S37" s="16"/>
     </row>
-    <row r="38" spans="1:19" ht="30">
+    <row r="38" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -16576,15 +16602,17 @@
         <v>29</v>
       </c>
       <c r="C38" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D38" s="51" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F38" s="66"/>
+        <v>130</v>
+      </c>
+      <c r="F38" s="65">
+        <v>123906.61</v>
+      </c>
       <c r="G38" s="11" t="s">
         <v>38</v>
       </c>
@@ -16603,7 +16631,7 @@
       <c r="R38" s="11"/>
       <c r="S38" s="16"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -16611,15 +16639,15 @@
         <v>29</v>
       </c>
       <c r="C39" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="F39" s="66">
+        <v>132</v>
+      </c>
+      <c r="F39" s="65">
         <v>111534.19</v>
       </c>
       <c r="G39" s="11" t="s">
@@ -16640,7 +16668,7 @@
       <c r="R39" s="11"/>
       <c r="S39" s="16"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -16648,15 +16676,15 @@
         <v>29</v>
       </c>
       <c r="C40" s="52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="F40" s="66">
+        <v>133</v>
+      </c>
+      <c r="F40" s="65">
         <v>146280</v>
       </c>
       <c r="G40" s="11" t="s">
@@ -16677,7 +16705,7 @@
       <c r="R40" s="11"/>
       <c r="S40" s="16"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -16685,13 +16713,13 @@
         <v>29</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F41" s="17">
         <v>35000</v>
@@ -16704,7 +16732,7 @@
       </c>
       <c r="I41" s="13"/>
       <c r="J41" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K41" s="14"/>
       <c r="L41" s="14"/>
@@ -16722,7 +16750,7 @@
       </c>
       <c r="S41" s="16"/>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -16730,13 +16758,13 @@
         <v>29</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F42" s="17">
         <v>35000</v>
@@ -16749,7 +16777,7 @@
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
@@ -16761,7 +16789,7 @@
       <c r="R42" s="11"/>
       <c r="S42" s="16"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -16769,13 +16797,13 @@
         <v>29</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F43" s="17">
         <v>35000</v>
@@ -16788,7 +16816,7 @@
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K43" s="14"/>
       <c r="L43" s="14"/>
@@ -16800,7 +16828,7 @@
       <c r="R43" s="11"/>
       <c r="S43" s="16"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -16808,13 +16836,13 @@
         <v>29</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F44" s="17">
         <v>35000</v>
@@ -16827,7 +16855,7 @@
       </c>
       <c r="I44" s="13"/>
       <c r="J44" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K44" s="14"/>
       <c r="L44" s="14"/>
@@ -16839,7 +16867,7 @@
       <c r="R44" s="11"/>
       <c r="S44" s="16"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -16847,13 +16875,13 @@
         <v>29</v>
       </c>
       <c r="C45" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="18" t="s">
         <v>140</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>147</v>
       </c>
       <c r="F45" s="17">
         <v>35000</v>
@@ -16866,7 +16894,7 @@
       </c>
       <c r="I45" s="13"/>
       <c r="J45" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
@@ -16878,7 +16906,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="16"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -16886,13 +16914,13 @@
         <v>29</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D46" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="18" t="s">
         <v>141</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>148</v>
       </c>
       <c r="F46" s="17">
         <v>35000</v>
@@ -16905,7 +16933,7 @@
       </c>
       <c r="I46" s="13"/>
       <c r="J46" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K46" s="14"/>
       <c r="L46" s="14"/>
@@ -16917,7 +16945,7 @@
       <c r="R46" s="11"/>
       <c r="S46" s="16"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -16925,13 +16953,13 @@
         <v>29</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F47" s="17">
         <v>35000</v>
@@ -16944,7 +16972,7 @@
       </c>
       <c r="I47" s="13"/>
       <c r="J47" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K47" s="14"/>
       <c r="L47" s="14"/>
@@ -16956,7 +16984,7 @@
       <c r="R47" s="11"/>
       <c r="S47" s="16"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -16964,13 +16992,13 @@
         <v>29</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F48" s="17">
         <v>35000</v>
@@ -16983,7 +17011,7 @@
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K48" s="14"/>
       <c r="L48" s="14"/>
@@ -16995,7 +17023,7 @@
       <c r="R48" s="11"/>
       <c r="S48" s="16"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -17003,13 +17031,13 @@
         <v>29</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F49" s="17">
         <v>35000</v>
@@ -17022,7 +17050,7 @@
       </c>
       <c r="I49" s="16"/>
       <c r="J49" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K49" s="14"/>
       <c r="L49" s="14"/>
@@ -17034,7 +17062,7 @@
       <c r="R49" s="11"/>
       <c r="S49" s="16"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -17042,13 +17070,13 @@
         <v>29</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F50" s="17">
         <v>35000</v>
@@ -17061,7 +17089,7 @@
       </c>
       <c r="I50" s="16"/>
       <c r="J50" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
@@ -17073,7 +17101,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="16"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -17081,13 +17109,13 @@
         <v>29</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F51" s="17">
         <v>35000</v>
@@ -17100,7 +17128,7 @@
       </c>
       <c r="I51" s="16"/>
       <c r="J51" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
@@ -17112,7 +17140,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="16"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -17120,13 +17148,13 @@
         <v>29</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F52" s="17">
         <v>35000</v>
@@ -17139,7 +17167,7 @@
       </c>
       <c r="I52" s="16"/>
       <c r="J52" s="37" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>
@@ -17157,7 +17185,7 @@
       </c>
       <c r="S52" s="16"/>
     </row>
-    <row r="53" spans="1:19" ht="29.25">
+    <row r="53" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -17165,13 +17193,13 @@
         <v>29</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F53" s="20">
         <v>29000</v>
@@ -17184,7 +17212,7 @@
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="43" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
@@ -17196,30 +17224,52 @@
       <c r="R53" s="11"/>
       <c r="S53" s="16"/>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="13"/>
+      <c r="B54" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="F54" s="20">
+        <v>2541</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="13">
+        <v>242</v>
+      </c>
       <c r="I54" s="16"/>
-      <c r="J54" s="43"/>
+      <c r="J54" s="43" t="s">
+        <v>101</v>
+      </c>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
       <c r="M54" s="11"/>
       <c r="N54" s="13"/>
       <c r="O54" s="13"/>
-      <c r="P54" s="11"/>
-      <c r="Q54" s="11"/>
-      <c r="R54" s="11"/>
+      <c r="P54" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q54" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="R54" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="S54" s="16"/>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -17242,7 +17292,7 @@
       <c r="R55" s="11"/>
       <c r="S55" s="16"/>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -17265,7 +17315,7 @@
       <c r="R56" s="11"/>
       <c r="S56" s="16"/>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -17288,7 +17338,7 @@
       <c r="R57" s="11"/>
       <c r="S57" s="16"/>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -17311,7 +17361,7 @@
       <c r="R58" s="11"/>
       <c r="S58" s="16"/>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -17334,7 +17384,7 @@
       <c r="R59" s="11"/>
       <c r="S59" s="16"/>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -17357,7 +17407,7 @@
       <c r="R60" s="11"/>
       <c r="S60" s="16"/>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -17380,7 +17430,7 @@
       <c r="R61" s="11"/>
       <c r="S61" s="16"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -17403,7 +17453,7 @@
       <c r="R62" s="11"/>
       <c r="S62" s="16"/>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -17426,7 +17476,7 @@
       <c r="R63" s="11"/>
       <c r="S63" s="16"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -17449,7 +17499,7 @@
       <c r="R64" s="11"/>
       <c r="S64" s="16"/>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -17472,7 +17522,7 @@
       <c r="R65" s="11"/>
       <c r="S65" s="16"/>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -17495,7 +17545,7 @@
       <c r="R66" s="11"/>
       <c r="S66" s="16"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -17518,7 +17568,7 @@
       <c r="R67" s="11"/>
       <c r="S67" s="16"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -17541,7 +17591,7 @@
       <c r="R68" s="11"/>
       <c r="S68" s="16"/>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -17564,7 +17614,7 @@
       <c r="R69" s="11"/>
       <c r="S69" s="16"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -17587,7 +17637,7 @@
       <c r="R70" s="11"/>
       <c r="S70" s="16"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -17610,7 +17660,7 @@
       <c r="R71" s="11"/>
       <c r="S71" s="16"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -17633,7 +17683,7 @@
       <c r="R72" s="11"/>
       <c r="S72" s="16"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -17656,7 +17706,7 @@
       <c r="R73" s="11"/>
       <c r="S73" s="16"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -17679,7 +17729,7 @@
       <c r="R74" s="11"/>
       <c r="S74" s="16"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -17702,7 +17752,7 @@
       <c r="R75" s="11"/>
       <c r="S75" s="16"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -17725,7 +17775,7 @@
       <c r="R76" s="11"/>
       <c r="S76" s="16"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -17748,7 +17798,7 @@
       <c r="R77" s="11"/>
       <c r="S77" s="16"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -17771,7 +17821,7 @@
       <c r="R78" s="11"/>
       <c r="S78" s="16"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -17794,7 +17844,7 @@
       <c r="R79" s="11"/>
       <c r="S79" s="16"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -17817,7 +17867,7 @@
       <c r="R80" s="11"/>
       <c r="S80" s="16"/>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -17840,7 +17890,7 @@
       <c r="R81" s="11"/>
       <c r="S81" s="16"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -17863,7 +17913,7 @@
       <c r="R82" s="11"/>
       <c r="S82" s="16"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -17886,7 +17936,7 @@
       <c r="R83" s="11"/>
       <c r="S83" s="16"/>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -17909,7 +17959,7 @@
       <c r="R84" s="11"/>
       <c r="S84" s="16"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -17932,7 +17982,7 @@
       <c r="R85" s="11"/>
       <c r="S85" s="16"/>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -17955,7 +18005,7 @@
       <c r="R86" s="11"/>
       <c r="S86" s="16"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -17978,7 +18028,7 @@
       <c r="R87" s="11"/>
       <c r="S87" s="16"/>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -18001,7 +18051,7 @@
       <c r="R88" s="11"/>
       <c r="S88" s="16"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -18024,7 +18074,7 @@
       <c r="R89" s="11"/>
       <c r="S89" s="16"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -18047,7 +18097,7 @@
       <c r="R90" s="11"/>
       <c r="S90" s="16"/>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -18070,7 +18120,7 @@
       <c r="R91" s="11"/>
       <c r="S91" s="16"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -18093,7 +18143,7 @@
       <c r="R92" s="11"/>
       <c r="S92" s="16"/>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -18116,7 +18166,7 @@
       <c r="R93" s="11"/>
       <c r="S93" s="16"/>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -18139,7 +18189,7 @@
       <c r="R94" s="11"/>
       <c r="S94" s="16"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -18162,7 +18212,7 @@
       <c r="R95" s="11"/>
       <c r="S95" s="16"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -18185,7 +18235,7 @@
       <c r="R96" s="11"/>
       <c r="S96" s="16"/>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -18208,7 +18258,7 @@
       <c r="R97" s="11"/>
       <c r="S97" s="16"/>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -18231,7 +18281,7 @@
       <c r="R98" s="11"/>
       <c r="S98" s="16"/>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -18254,7 +18304,7 @@
       <c r="R99" s="11"/>
       <c r="S99" s="16"/>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -18277,7 +18327,7 @@
       <c r="R100" s="11"/>
       <c r="S100" s="16"/>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -18300,7 +18350,7 @@
       <c r="R101" s="11"/>
       <c r="S101" s="16"/>
     </row>
-    <row r="102" spans="1:19">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -18323,7 +18373,7 @@
       <c r="R102" s="11"/>
       <c r="S102" s="16"/>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -18346,7 +18396,7 @@
       <c r="R103" s="11"/>
       <c r="S103" s="16"/>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -18369,7 +18419,7 @@
       <c r="R104" s="11"/>
       <c r="S104" s="16"/>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -18392,7 +18442,7 @@
       <c r="R105" s="11"/>
       <c r="S105" s="16"/>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -18415,7 +18465,7 @@
       <c r="R106" s="11"/>
       <c r="S106" s="16"/>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -18438,7 +18488,7 @@
       <c r="R107" s="11"/>
       <c r="S107" s="16"/>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -18461,7 +18511,7 @@
       <c r="R108" s="11"/>
       <c r="S108" s="16"/>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -18484,7 +18534,7 @@
       <c r="R109" s="11"/>
       <c r="S109" s="16"/>
     </row>
-    <row r="110" spans="1:19">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -18507,7 +18557,7 @@
       <c r="R110" s="11"/>
       <c r="S110" s="16"/>
     </row>
-    <row r="111" spans="1:19">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -18530,7 +18580,7 @@
       <c r="R111" s="11"/>
       <c r="S111" s="16"/>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -18553,7 +18603,7 @@
       <c r="R112" s="11"/>
       <c r="S112" s="16"/>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -18576,7 +18626,7 @@
       <c r="R113" s="11"/>
       <c r="S113" s="16"/>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -18599,7 +18649,7 @@
       <c r="R114" s="11"/>
       <c r="S114" s="16"/>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -18622,7 +18672,7 @@
       <c r="R115" s="11"/>
       <c r="S115" s="16"/>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -18645,7 +18695,7 @@
       <c r="R116" s="11"/>
       <c r="S116" s="16"/>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -18668,7 +18718,7 @@
       <c r="R117" s="11"/>
       <c r="S117" s="16"/>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -18691,7 +18741,7 @@
       <c r="R118" s="11"/>
       <c r="S118" s="16"/>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -18714,7 +18764,7 @@
       <c r="R119" s="11"/>
       <c r="S119" s="16"/>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -18737,7 +18787,7 @@
       <c r="R120" s="11"/>
       <c r="S120" s="16"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -18760,7 +18810,7 @@
       <c r="R121" s="11"/>
       <c r="S121" s="16"/>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -18783,7 +18833,7 @@
       <c r="R122" s="11"/>
       <c r="S122" s="16"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -18806,7 +18856,7 @@
       <c r="R123" s="11"/>
       <c r="S123" s="16"/>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -18829,7 +18879,7 @@
       <c r="R124" s="11"/>
       <c r="S124" s="16"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -18852,7 +18902,7 @@
       <c r="R125" s="11"/>
       <c r="S125" s="16"/>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -18875,7 +18925,7 @@
       <c r="R126" s="11"/>
       <c r="S126" s="16"/>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -18898,7 +18948,7 @@
       <c r="R127" s="11"/>
       <c r="S127" s="16"/>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -18921,7 +18971,7 @@
       <c r="R128" s="11"/>
       <c r="S128" s="16"/>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -18944,7 +18994,7 @@
       <c r="R129" s="11"/>
       <c r="S129" s="16"/>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -18967,7 +19017,7 @@
       <c r="R130" s="11"/>
       <c r="S130" s="16"/>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -18990,7 +19040,7 @@
       <c r="R131" s="11"/>
       <c r="S131" s="16"/>
     </row>
-    <row r="132" spans="1:19">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -19013,7 +19063,7 @@
       <c r="R132" s="11"/>
       <c r="S132" s="16"/>
     </row>
-    <row r="133" spans="1:19">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -19036,7 +19086,7 @@
       <c r="R133" s="11"/>
       <c r="S133" s="16"/>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -19059,7 +19109,7 @@
       <c r="R134" s="11"/>
       <c r="S134" s="16"/>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -19082,7 +19132,7 @@
       <c r="R135" s="11"/>
       <c r="S135" s="16"/>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -19105,7 +19155,7 @@
       <c r="R136" s="11"/>
       <c r="S136" s="16"/>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -19128,7 +19178,7 @@
       <c r="R137" s="11"/>
       <c r="S137" s="16"/>
     </row>
-    <row r="138" spans="1:19">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -19151,7 +19201,7 @@
       <c r="R138" s="11"/>
       <c r="S138" s="16"/>
     </row>
-    <row r="139" spans="1:19">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -19174,7 +19224,7 @@
       <c r="R139" s="11"/>
       <c r="S139" s="16"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -19197,7 +19247,7 @@
       <c r="R140" s="11"/>
       <c r="S140" s="16"/>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -19220,7 +19270,7 @@
       <c r="R141" s="11"/>
       <c r="S141" s="16"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -19243,7 +19293,7 @@
       <c r="R142" s="11"/>
       <c r="S142" s="16"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -19266,7 +19316,7 @@
       <c r="R143" s="11"/>
       <c r="S143" s="16"/>
     </row>
-    <row r="144" spans="1:19">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -19289,7 +19339,7 @@
       <c r="R144" s="11"/>
       <c r="S144" s="16"/>
     </row>
-    <row r="145" spans="1:19">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -19312,7 +19362,7 @@
       <c r="R145" s="11"/>
       <c r="S145" s="16"/>
     </row>
-    <row r="146" spans="1:19">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -19335,7 +19385,7 @@
       <c r="R146" s="11"/>
       <c r="S146" s="16"/>
     </row>
-    <row r="147" spans="1:19">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -19358,7 +19408,7 @@
       <c r="R147" s="11"/>
       <c r="S147" s="16"/>
     </row>
-    <row r="148" spans="1:19">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -19381,7 +19431,7 @@
       <c r="R148" s="11"/>
       <c r="S148" s="16"/>
     </row>
-    <row r="149" spans="1:19">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -19404,7 +19454,7 @@
       <c r="R149" s="11"/>
       <c r="S149" s="16"/>
     </row>
-    <row r="150" spans="1:19">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -19427,7 +19477,7 @@
       <c r="R150" s="11"/>
       <c r="S150" s="16"/>
     </row>
-    <row r="151" spans="1:19">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -19450,7 +19500,7 @@
       <c r="R151" s="11"/>
       <c r="S151" s="16"/>
     </row>
-    <row r="152" spans="1:19">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -19473,7 +19523,7 @@
       <c r="R152" s="11"/>
       <c r="S152" s="16"/>
     </row>
-    <row r="153" spans="1:19">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -19496,7 +19546,7 @@
       <c r="R153" s="11"/>
       <c r="S153" s="16"/>
     </row>
-    <row r="154" spans="1:19">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -19519,7 +19569,7 @@
       <c r="R154" s="11"/>
       <c r="S154" s="16"/>
     </row>
-    <row r="155" spans="1:19">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -19542,7 +19592,7 @@
       <c r="R155" s="11"/>
       <c r="S155" s="16"/>
     </row>
-    <row r="156" spans="1:19">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -19565,7 +19615,7 @@
       <c r="R156" s="11"/>
       <c r="S156" s="16"/>
     </row>
-    <row r="157" spans="1:19">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -19588,7 +19638,7 @@
       <c r="R157" s="11"/>
       <c r="S157" s="16"/>
     </row>
-    <row r="158" spans="1:19">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -19611,7 +19661,7 @@
       <c r="R158" s="11"/>
       <c r="S158" s="16"/>
     </row>
-    <row r="159" spans="1:19">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -19634,7 +19684,7 @@
       <c r="R159" s="11"/>
       <c r="S159" s="16"/>
     </row>
-    <row r="160" spans="1:19">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -19657,7 +19707,7 @@
       <c r="R160" s="11"/>
       <c r="S160" s="16"/>
     </row>
-    <row r="161" spans="1:19">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -19680,7 +19730,7 @@
       <c r="R161" s="11"/>
       <c r="S161" s="16"/>
     </row>
-    <row r="162" spans="1:19">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -19703,7 +19753,7 @@
       <c r="R162" s="11"/>
       <c r="S162" s="16"/>
     </row>
-    <row r="163" spans="1:19">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -19726,7 +19776,7 @@
       <c r="R163" s="11"/>
       <c r="S163" s="16"/>
     </row>
-    <row r="164" spans="1:19">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -19749,7 +19799,7 @@
       <c r="R164" s="11"/>
       <c r="S164" s="16"/>
     </row>
-    <row r="165" spans="1:19">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -19772,7 +19822,7 @@
       <c r="R165" s="11"/>
       <c r="S165" s="16"/>
     </row>
-    <row r="166" spans="1:19">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -19795,7 +19845,7 @@
       <c r="R166" s="11"/>
       <c r="S166" s="16"/>
     </row>
-    <row r="167" spans="1:19">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -19818,7 +19868,7 @@
       <c r="R167" s="11"/>
       <c r="S167" s="16"/>
     </row>
-    <row r="168" spans="1:19">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -19841,7 +19891,7 @@
       <c r="R168" s="11"/>
       <c r="S168" s="16"/>
     </row>
-    <row r="169" spans="1:19">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -19864,7 +19914,7 @@
       <c r="R169" s="11"/>
       <c r="S169" s="16"/>
     </row>
-    <row r="170" spans="1:19">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -19887,7 +19937,7 @@
       <c r="R170" s="11"/>
       <c r="S170" s="16"/>
     </row>
-    <row r="171" spans="1:19">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -19910,7 +19960,7 @@
       <c r="R171" s="11"/>
       <c r="S171" s="16"/>
     </row>
-    <row r="172" spans="1:19">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -19933,7 +19983,7 @@
       <c r="R172" s="11"/>
       <c r="S172" s="16"/>
     </row>
-    <row r="173" spans="1:19">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -19956,7 +20006,7 @@
       <c r="R173" s="11"/>
       <c r="S173" s="16"/>
     </row>
-    <row r="174" spans="1:19">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -19979,7 +20029,7 @@
       <c r="R174" s="11"/>
       <c r="S174" s="16"/>
     </row>
-    <row r="175" spans="1:19">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>174</v>
       </c>
@@ -20002,7 +20052,7 @@
       <c r="R175" s="11"/>
       <c r="S175" s="16"/>
     </row>
-    <row r="176" spans="1:19">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -20025,7 +20075,7 @@
       <c r="R176" s="11"/>
       <c r="S176" s="16"/>
     </row>
-    <row r="177" spans="1:19">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -20048,7 +20098,7 @@
       <c r="R177" s="11"/>
       <c r="S177" s="16"/>
     </row>
-    <row r="178" spans="1:19">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -20071,7 +20121,7 @@
       <c r="R178" s="11"/>
       <c r="S178" s="16"/>
     </row>
-    <row r="179" spans="1:19">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>178</v>
       </c>
@@ -20094,7 +20144,7 @@
       <c r="R179" s="11"/>
       <c r="S179" s="16"/>
     </row>
-    <row r="180" spans="1:19">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -20117,7 +20167,7 @@
       <c r="R180" s="11"/>
       <c r="S180" s="16"/>
     </row>
-    <row r="181" spans="1:19">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>180</v>
       </c>
@@ -20140,7 +20190,7 @@
       <c r="R181" s="11"/>
       <c r="S181" s="16"/>
     </row>
-    <row r="182" spans="1:19">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -20163,7 +20213,7 @@
       <c r="R182" s="11"/>
       <c r="S182" s="16"/>
     </row>
-    <row r="183" spans="1:19">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>182</v>
       </c>
@@ -20186,7 +20236,7 @@
       <c r="R183" s="11"/>
       <c r="S183" s="16"/>
     </row>
-    <row r="184" spans="1:19">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -20209,7 +20259,7 @@
       <c r="R184" s="11"/>
       <c r="S184" s="16"/>
     </row>
-    <row r="185" spans="1:19">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>184</v>
       </c>
@@ -20232,7 +20282,7 @@
       <c r="R185" s="11"/>
       <c r="S185" s="16"/>
     </row>
-    <row r="186" spans="1:19">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>185</v>
       </c>
@@ -20255,7 +20305,7 @@
       <c r="R186" s="11"/>
       <c r="S186" s="16"/>
     </row>
-    <row r="187" spans="1:19">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>186</v>
       </c>
@@ -20278,7 +20328,7 @@
       <c r="R187" s="11"/>
       <c r="S187" s="16"/>
     </row>
-    <row r="188" spans="1:19">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>187</v>
       </c>
@@ -20301,7 +20351,7 @@
       <c r="R188" s="11"/>
       <c r="S188" s="16"/>
     </row>
-    <row r="189" spans="1:19">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>188</v>
       </c>
@@ -20324,7 +20374,7 @@
       <c r="R189" s="11"/>
       <c r="S189" s="16"/>
     </row>
-    <row r="190" spans="1:19">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>189</v>
       </c>
@@ -20347,7 +20397,7 @@
       <c r="R190" s="11"/>
       <c r="S190" s="16"/>
     </row>
-    <row r="191" spans="1:19">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>190</v>
       </c>
@@ -20370,7 +20420,7 @@
       <c r="R191" s="11"/>
       <c r="S191" s="16"/>
     </row>
-    <row r="192" spans="1:19">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>191</v>
       </c>
@@ -20393,7 +20443,7 @@
       <c r="R192" s="11"/>
       <c r="S192" s="16"/>
     </row>
-    <row r="193" spans="1:19">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>192</v>
       </c>
@@ -20416,7 +20466,7 @@
       <c r="R193" s="11"/>
       <c r="S193" s="16"/>
     </row>
-    <row r="194" spans="1:19">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -20439,7 +20489,7 @@
       <c r="R194" s="11"/>
       <c r="S194" s="16"/>
     </row>
-    <row r="195" spans="1:19">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>194</v>
       </c>
@@ -20462,7 +20512,7 @@
       <c r="R195" s="11"/>
       <c r="S195" s="16"/>
     </row>
-    <row r="196" spans="1:19">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -20485,7 +20535,7 @@
       <c r="R196" s="11"/>
       <c r="S196" s="16"/>
     </row>
-    <row r="197" spans="1:19">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -20508,7 +20558,7 @@
       <c r="R197" s="11"/>
       <c r="S197" s="16"/>
     </row>
-    <row r="198" spans="1:19">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -20531,7 +20581,7 @@
       <c r="R198" s="11"/>
       <c r="S198" s="16"/>
     </row>
-    <row r="199" spans="1:19">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>198</v>
       </c>
@@ -20554,7 +20604,7 @@
       <c r="R199" s="11"/>
       <c r="S199" s="16"/>
     </row>
-    <row r="200" spans="1:19">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -20577,7 +20627,7 @@
       <c r="R200" s="11"/>
       <c r="S200" s="16"/>
     </row>
-    <row r="201" spans="1:19">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>200</v>
       </c>
@@ -20600,7 +20650,7 @@
       <c r="R201" s="11"/>
       <c r="S201" s="16"/>
     </row>
-    <row r="202" spans="1:19">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>201</v>
       </c>
@@ -20623,7 +20673,7 @@
       <c r="R202" s="11"/>
       <c r="S202" s="16"/>
     </row>
-    <row r="203" spans="1:19">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>202</v>
       </c>
@@ -20646,7 +20696,7 @@
       <c r="R203" s="11"/>
       <c r="S203" s="16"/>
     </row>
-    <row r="204" spans="1:19">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>203</v>
       </c>
@@ -20669,7 +20719,7 @@
       <c r="R204" s="11"/>
       <c r="S204" s="16"/>
     </row>
-    <row r="205" spans="1:19">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>204</v>
       </c>
@@ -20692,7 +20742,7 @@
       <c r="R205" s="11"/>
       <c r="S205" s="16"/>
     </row>
-    <row r="206" spans="1:19">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>205</v>
       </c>
@@ -20715,7 +20765,7 @@
       <c r="R206" s="11"/>
       <c r="S206" s="16"/>
     </row>
-    <row r="207" spans="1:19">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>206</v>
       </c>
@@ -20738,7 +20788,7 @@
       <c r="R207" s="11"/>
       <c r="S207" s="16"/>
     </row>
-    <row r="208" spans="1:19">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>207</v>
       </c>
@@ -20761,7 +20811,7 @@
       <c r="R208" s="11"/>
       <c r="S208" s="16"/>
     </row>
-    <row r="209" spans="1:19">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>208</v>
       </c>
@@ -20784,7 +20834,7 @@
       <c r="R209" s="11"/>
       <c r="S209" s="16"/>
     </row>
-    <row r="210" spans="1:19">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -20807,7 +20857,7 @@
       <c r="R210" s="11"/>
       <c r="S210" s="16"/>
     </row>
-    <row r="211" spans="1:19">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>210</v>
       </c>
@@ -20830,7 +20880,7 @@
       <c r="R211" s="11"/>
       <c r="S211" s="16"/>
     </row>
-    <row r="212" spans="1:19">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -20853,7 +20903,7 @@
       <c r="R212" s="11"/>
       <c r="S212" s="16"/>
     </row>
-    <row r="213" spans="1:19">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>212</v>
       </c>
@@ -20876,7 +20926,7 @@
       <c r="R213" s="11"/>
       <c r="S213" s="16"/>
     </row>
-    <row r="214" spans="1:19">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -20899,7 +20949,7 @@
       <c r="R214" s="11"/>
       <c r="S214" s="16"/>
     </row>
-    <row r="215" spans="1:19">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>214</v>
       </c>
@@ -20922,7 +20972,7 @@
       <c r="R215" s="11"/>
       <c r="S215" s="16"/>
     </row>
-    <row r="216" spans="1:19">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -20945,7 +20995,7 @@
       <c r="R216" s="11"/>
       <c r="S216" s="16"/>
     </row>
-    <row r="217" spans="1:19">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>216</v>
       </c>
@@ -20968,7 +21018,7 @@
       <c r="R217" s="11"/>
       <c r="S217" s="16"/>
     </row>
-    <row r="218" spans="1:19">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -20991,7 +21041,7 @@
       <c r="R218" s="11"/>
       <c r="S218" s="16"/>
     </row>
-    <row r="219" spans="1:19">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>218</v>
       </c>
@@ -21014,7 +21064,7 @@
       <c r="R219" s="11"/>
       <c r="S219" s="16"/>
     </row>
-    <row r="220" spans="1:19">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -21037,7 +21087,7 @@
       <c r="R220" s="11"/>
       <c r="S220" s="16"/>
     </row>
-    <row r="221" spans="1:19">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>220</v>
       </c>
@@ -21060,7 +21110,7 @@
       <c r="R221" s="11"/>
       <c r="S221" s="16"/>
     </row>
-    <row r="222" spans="1:19">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -21083,7 +21133,7 @@
       <c r="R222" s="11"/>
       <c r="S222" s="16"/>
     </row>
-    <row r="223" spans="1:19">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>222</v>
       </c>
@@ -21106,7 +21156,7 @@
       <c r="R223" s="11"/>
       <c r="S223" s="16"/>
     </row>
-    <row r="224" spans="1:19">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -21129,7 +21179,7 @@
       <c r="R224" s="11"/>
       <c r="S224" s="16"/>
     </row>
-    <row r="225" spans="1:19">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -21152,7 +21202,7 @@
       <c r="R225" s="11"/>
       <c r="S225" s="16"/>
     </row>
-    <row r="226" spans="1:19">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -21175,7 +21225,7 @@
       <c r="R226" s="11"/>
       <c r="S226" s="16"/>
     </row>
-    <row r="227" spans="1:19">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>226</v>
       </c>
@@ -21198,7 +21248,7 @@
       <c r="R227" s="11"/>
       <c r="S227" s="16"/>
     </row>
-    <row r="228" spans="1:19">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>227</v>
       </c>
@@ -21221,7 +21271,7 @@
       <c r="R228" s="11"/>
       <c r="S228" s="16"/>
     </row>
-    <row r="229" spans="1:19">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>228</v>
       </c>
@@ -21244,7 +21294,7 @@
       <c r="R229" s="11"/>
       <c r="S229" s="16"/>
     </row>
-    <row r="230" spans="1:19">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>229</v>
       </c>
@@ -21267,7 +21317,7 @@
       <c r="R230" s="11"/>
       <c r="S230" s="16"/>
     </row>
-    <row r="231" spans="1:19">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>230</v>
       </c>
@@ -21290,7 +21340,7 @@
       <c r="R231" s="11"/>
       <c r="S231" s="16"/>
     </row>
-    <row r="232" spans="1:19">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -21313,7 +21363,7 @@
       <c r="R232" s="11"/>
       <c r="S232" s="16"/>
     </row>
-    <row r="233" spans="1:19">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>232</v>
       </c>
@@ -21336,7 +21386,7 @@
       <c r="R233" s="11"/>
       <c r="S233" s="16"/>
     </row>
-    <row r="234" spans="1:19">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -21359,7 +21409,7 @@
       <c r="R234" s="11"/>
       <c r="S234" s="16"/>
     </row>
-    <row r="235" spans="1:19">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>234</v>
       </c>
@@ -21382,7 +21432,7 @@
       <c r="R235" s="11"/>
       <c r="S235" s="16"/>
     </row>
-    <row r="236" spans="1:19">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -21405,7 +21455,7 @@
       <c r="R236" s="11"/>
       <c r="S236" s="16"/>
     </row>
-    <row r="237" spans="1:19">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>236</v>
       </c>
@@ -21428,7 +21478,7 @@
       <c r="R237" s="11"/>
       <c r="S237" s="16"/>
     </row>
-    <row r="238" spans="1:19">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -21451,7 +21501,7 @@
       <c r="R238" s="11"/>
       <c r="S238" s="16"/>
     </row>
-    <row r="239" spans="1:19">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>238</v>
       </c>
@@ -21474,7 +21524,7 @@
       <c r="R239" s="11"/>
       <c r="S239" s="16"/>
     </row>
-    <row r="240" spans="1:19">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -21497,7 +21547,7 @@
       <c r="R240" s="11"/>
       <c r="S240" s="16"/>
     </row>
-    <row r="241" spans="1:19">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>240</v>
       </c>
@@ -21520,7 +21570,7 @@
       <c r="R241" s="11"/>
       <c r="S241" s="16"/>
     </row>
-    <row r="242" spans="1:19">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -21543,7 +21593,7 @@
       <c r="R242" s="11"/>
       <c r="S242" s="16"/>
     </row>
-    <row r="243" spans="1:19">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>242</v>
       </c>
@@ -21566,7 +21616,7 @@
       <c r="R243" s="11"/>
       <c r="S243" s="16"/>
     </row>
-    <row r="244" spans="1:19">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -21589,7 +21639,7 @@
       <c r="R244" s="11"/>
       <c r="S244" s="16"/>
     </row>
-    <row r="245" spans="1:19">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>244</v>
       </c>
@@ -21612,7 +21662,7 @@
       <c r="R245" s="11"/>
       <c r="S245" s="16"/>
     </row>
-    <row r="246" spans="1:19">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -21635,7 +21685,7 @@
       <c r="R246" s="11"/>
       <c r="S246" s="16"/>
     </row>
-    <row r="247" spans="1:19">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>246</v>
       </c>
@@ -21658,7 +21708,7 @@
       <c r="R247" s="11"/>
       <c r="S247" s="16"/>
     </row>
-    <row r="248" spans="1:19">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -21681,7 +21731,7 @@
       <c r="R248" s="11"/>
       <c r="S248" s="16"/>
     </row>
-    <row r="249" spans="1:19">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>248</v>
       </c>
@@ -21704,7 +21754,7 @@
       <c r="R249" s="11"/>
       <c r="S249" s="16"/>
     </row>
-    <row r="250" spans="1:19">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>249</v>
       </c>
@@ -21727,7 +21777,7 @@
       <c r="R250" s="11"/>
       <c r="S250" s="16"/>
     </row>
-    <row r="251" spans="1:19">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>250</v>
       </c>
@@ -21750,7 +21800,7 @@
       <c r="R251" s="11"/>
       <c r="S251" s="16"/>
     </row>
-    <row r="252" spans="1:19">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>251</v>
       </c>
@@ -21773,7 +21823,7 @@
       <c r="R252" s="11"/>
       <c r="S252" s="16"/>
     </row>
-    <row r="253" spans="1:19">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>252</v>
       </c>
@@ -21796,7 +21846,7 @@
       <c r="R253" s="11"/>
       <c r="S253" s="16"/>
     </row>
-    <row r="254" spans="1:19">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>253</v>
       </c>
@@ -21819,7 +21869,7 @@
       <c r="R254" s="11"/>
       <c r="S254" s="16"/>
     </row>
-    <row r="255" spans="1:19">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>254</v>
       </c>
@@ -21842,7 +21892,7 @@
       <c r="R255" s="11"/>
       <c r="S255" s="16"/>
     </row>
-    <row r="256" spans="1:19">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>255</v>
       </c>
@@ -21865,7 +21915,7 @@
       <c r="R256" s="11"/>
       <c r="S256" s="16"/>
     </row>
-    <row r="257" spans="1:19">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>256</v>
       </c>
@@ -21888,7 +21938,7 @@
       <c r="R257" s="11"/>
       <c r="S257" s="16"/>
     </row>
-    <row r="258" spans="1:19">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>257</v>
       </c>
@@ -21911,7 +21961,7 @@
       <c r="R258" s="11"/>
       <c r="S258" s="16"/>
     </row>
-    <row r="259" spans="1:19">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>258</v>
       </c>
@@ -21934,7 +21984,7 @@
       <c r="R259" s="11"/>
       <c r="S259" s="16"/>
     </row>
-    <row r="260" spans="1:19">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>259</v>
       </c>
@@ -21957,7 +22007,7 @@
       <c r="R260" s="11"/>
       <c r="S260" s="16"/>
     </row>
-    <row r="261" spans="1:19">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>260</v>
       </c>
@@ -21980,7 +22030,7 @@
       <c r="R261" s="11"/>
       <c r="S261" s="16"/>
     </row>
-    <row r="262" spans="1:19">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>261</v>
       </c>
@@ -22003,7 +22053,7 @@
       <c r="R262" s="11"/>
       <c r="S262" s="16"/>
     </row>
-    <row r="263" spans="1:19">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>262</v>
       </c>
@@ -22026,7 +22076,7 @@
       <c r="R263" s="11"/>
       <c r="S263" s="16"/>
     </row>
-    <row r="264" spans="1:19">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>263</v>
       </c>
@@ -22049,7 +22099,7 @@
       <c r="R264" s="11"/>
       <c r="S264" s="16"/>
     </row>
-    <row r="265" spans="1:19">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>264</v>
       </c>
@@ -22072,7 +22122,7 @@
       <c r="R265" s="11"/>
       <c r="S265" s="16"/>
     </row>
-    <row r="266" spans="1:19">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>265</v>
       </c>
@@ -22095,7 +22145,7 @@
       <c r="R266" s="11"/>
       <c r="S266" s="16"/>
     </row>
-    <row r="267" spans="1:19">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>266</v>
       </c>
@@ -22118,7 +22168,7 @@
       <c r="R267" s="11"/>
       <c r="S267" s="16"/>
     </row>
-    <row r="268" spans="1:19">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>267</v>
       </c>
@@ -22141,7 +22191,7 @@
       <c r="R268" s="11"/>
       <c r="S268" s="16"/>
     </row>
-    <row r="269" spans="1:19">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>268</v>
       </c>
@@ -22164,7 +22214,7 @@
       <c r="R269" s="11"/>
       <c r="S269" s="16"/>
     </row>
-    <row r="270" spans="1:19">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>269</v>
       </c>
@@ -22187,7 +22237,7 @@
       <c r="R270" s="11"/>
       <c r="S270" s="16"/>
     </row>
-    <row r="271" spans="1:19">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>270</v>
       </c>
@@ -22210,7 +22260,7 @@
       <c r="R271" s="11"/>
       <c r="S271" s="16"/>
     </row>
-    <row r="272" spans="1:19">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>271</v>
       </c>
@@ -22233,7 +22283,7 @@
       <c r="R272" s="11"/>
       <c r="S272" s="16"/>
     </row>
-    <row r="273" spans="1:19">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>272</v>
       </c>
@@ -22256,7 +22306,7 @@
       <c r="R273" s="11"/>
       <c r="S273" s="16"/>
     </row>
-    <row r="274" spans="1:19">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>273</v>
       </c>
@@ -22279,7 +22329,7 @@
       <c r="R274" s="11"/>
       <c r="S274" s="16"/>
     </row>
-    <row r="275" spans="1:19">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>274</v>
       </c>
@@ -22302,7 +22352,7 @@
       <c r="R275" s="11"/>
       <c r="S275" s="16"/>
     </row>
-    <row r="276" spans="1:19">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>275</v>
       </c>
@@ -22325,7 +22375,7 @@
       <c r="R276" s="11"/>
       <c r="S276" s="16"/>
     </row>
-    <row r="277" spans="1:19">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>276</v>
       </c>
@@ -22348,7 +22398,7 @@
       <c r="R277" s="11"/>
       <c r="S277" s="16"/>
     </row>
-    <row r="278" spans="1:19">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>277</v>
       </c>
@@ -22371,7 +22421,7 @@
       <c r="R278" s="11"/>
       <c r="S278" s="16"/>
     </row>
-    <row r="279" spans="1:19">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>278</v>
       </c>
@@ -22394,7 +22444,7 @@
       <c r="R279" s="11"/>
       <c r="S279" s="16"/>
     </row>
-    <row r="280" spans="1:19">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>279</v>
       </c>
@@ -22417,7 +22467,7 @@
       <c r="R280" s="11"/>
       <c r="S280" s="16"/>
     </row>
-    <row r="281" spans="1:19">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>280</v>
       </c>
@@ -22440,7 +22490,7 @@
       <c r="R281" s="11"/>
       <c r="S281" s="16"/>
     </row>
-    <row r="282" spans="1:19">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>281</v>
       </c>
@@ -22463,7 +22513,7 @@
       <c r="R282" s="11"/>
       <c r="S282" s="16"/>
     </row>
-    <row r="283" spans="1:19">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>282</v>
       </c>
@@ -22486,7 +22536,7 @@
       <c r="R283" s="11"/>
       <c r="S283" s="16"/>
     </row>
-    <row r="284" spans="1:19">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>283</v>
       </c>
@@ -22509,7 +22559,7 @@
       <c r="R284" s="11"/>
       <c r="S284" s="16"/>
     </row>
-    <row r="285" spans="1:19">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>284</v>
       </c>
@@ -22532,7 +22582,7 @@
       <c r="R285" s="11"/>
       <c r="S285" s="16"/>
     </row>
-    <row r="286" spans="1:19">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>285</v>
       </c>
@@ -22555,7 +22605,7 @@
       <c r="R286" s="11"/>
       <c r="S286" s="16"/>
     </row>
-    <row r="287" spans="1:19">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>286</v>
       </c>
@@ -22578,7 +22628,7 @@
       <c r="R287" s="11"/>
       <c r="S287" s="16"/>
     </row>
-    <row r="288" spans="1:19">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>287</v>
       </c>
@@ -22601,7 +22651,7 @@
       <c r="R288" s="11"/>
       <c r="S288" s="16"/>
     </row>
-    <row r="289" spans="1:19">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>288</v>
       </c>
@@ -22624,7 +22674,7 @@
       <c r="R289" s="11"/>
       <c r="S289" s="16"/>
     </row>
-    <row r="290" spans="1:19">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>289</v>
       </c>
@@ -22647,7 +22697,7 @@
       <c r="R290" s="11"/>
       <c r="S290" s="16"/>
     </row>
-    <row r="291" spans="1:19">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>290</v>
       </c>
@@ -22670,7 +22720,7 @@
       <c r="R291" s="11"/>
       <c r="S291" s="16"/>
     </row>
-    <row r="292" spans="1:19">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>291</v>
       </c>
@@ -22693,7 +22743,7 @@
       <c r="R292" s="11"/>
       <c r="S292" s="16"/>
     </row>
-    <row r="293" spans="1:19">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>292</v>
       </c>
@@ -22716,7 +22766,7 @@
       <c r="R293" s="11"/>
       <c r="S293" s="16"/>
     </row>
-    <row r="294" spans="1:19">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>293</v>
       </c>
@@ -22739,7 +22789,7 @@
       <c r="R294" s="11"/>
       <c r="S294" s="16"/>
     </row>
-    <row r="295" spans="1:19">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>294</v>
       </c>
@@ -22762,7 +22812,7 @@
       <c r="R295" s="11"/>
       <c r="S295" s="16"/>
     </row>
-    <row r="296" spans="1:19">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>295</v>
       </c>
@@ -22785,7 +22835,7 @@
       <c r="R296" s="11"/>
       <c r="S296" s="16"/>
     </row>
-    <row r="297" spans="1:19">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>296</v>
       </c>
@@ -22808,7 +22858,7 @@
       <c r="R297" s="11"/>
       <c r="S297" s="16"/>
     </row>
-    <row r="298" spans="1:19">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>297</v>
       </c>
@@ -22831,7 +22881,7 @@
       <c r="R298" s="11"/>
       <c r="S298" s="16"/>
     </row>
-    <row r="299" spans="1:19">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>298</v>
       </c>
@@ -22854,7 +22904,7 @@
       <c r="R299" s="11"/>
       <c r="S299" s="16"/>
     </row>
-    <row r="300" spans="1:19">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>299</v>
       </c>
@@ -22877,7 +22927,7 @@
       <c r="R300" s="11"/>
       <c r="S300" s="16"/>
     </row>
-    <row r="301" spans="1:19">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>300</v>
       </c>
@@ -22900,7 +22950,7 @@
       <c r="R301" s="11"/>
       <c r="S301" s="16"/>
     </row>
-    <row r="302" spans="1:19">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>301</v>
       </c>
@@ -22923,7 +22973,7 @@
       <c r="R302" s="11"/>
       <c r="S302" s="16"/>
     </row>
-    <row r="303" spans="1:19">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>302</v>
       </c>
@@ -22946,7 +22996,7 @@
       <c r="R303" s="11"/>
       <c r="S303" s="16"/>
     </row>
-    <row r="304" spans="1:19">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>303</v>
       </c>
@@ -22969,7 +23019,7 @@
       <c r="R304" s="11"/>
       <c r="S304" s="16"/>
     </row>
-    <row r="305" spans="1:19">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>304</v>
       </c>
@@ -22992,7 +23042,7 @@
       <c r="R305" s="11"/>
       <c r="S305" s="16"/>
     </row>
-    <row r="306" spans="1:19">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>305</v>
       </c>
@@ -23015,7 +23065,7 @@
       <c r="R306" s="11"/>
       <c r="S306" s="16"/>
     </row>
-    <row r="307" spans="1:19">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>306</v>
       </c>
@@ -23038,7 +23088,7 @@
       <c r="R307" s="11"/>
       <c r="S307" s="16"/>
     </row>
-    <row r="308" spans="1:19">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>307</v>
       </c>
@@ -23061,7 +23111,7 @@
       <c r="R308" s="11"/>
       <c r="S308" s="16"/>
     </row>
-    <row r="309" spans="1:19">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>308</v>
       </c>
@@ -23084,7 +23134,7 @@
       <c r="R309" s="11"/>
       <c r="S309" s="16"/>
     </row>
-    <row r="310" spans="1:19">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>309</v>
       </c>
@@ -23107,7 +23157,7 @@
       <c r="R310" s="11"/>
       <c r="S310" s="16"/>
     </row>
-    <row r="311" spans="1:19">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>310</v>
       </c>
@@ -23130,7 +23180,7 @@
       <c r="R311" s="11"/>
       <c r="S311" s="16"/>
     </row>
-    <row r="312" spans="1:19">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>311</v>
       </c>
@@ -23153,7 +23203,7 @@
       <c r="R312" s="11"/>
       <c r="S312" s="16"/>
     </row>
-    <row r="313" spans="1:19">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>312</v>
       </c>
@@ -23176,7 +23226,7 @@
       <c r="R313" s="11"/>
       <c r="S313" s="16"/>
     </row>
-    <row r="314" spans="1:19">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>313</v>
       </c>
@@ -23199,7 +23249,7 @@
       <c r="R314" s="11"/>
       <c r="S314" s="16"/>
     </row>
-    <row r="315" spans="1:19">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>314</v>
       </c>
@@ -23222,7 +23272,7 @@
       <c r="R315" s="11"/>
       <c r="S315" s="16"/>
     </row>
-    <row r="316" spans="1:19">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>315</v>
       </c>
@@ -23245,7 +23295,7 @@
       <c r="R316" s="11"/>
       <c r="S316" s="16"/>
     </row>
-    <row r="317" spans="1:19">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>316</v>
       </c>
@@ -23268,7 +23318,7 @@
       <c r="R317" s="11"/>
       <c r="S317" s="16"/>
     </row>
-    <row r="318" spans="1:19">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>317</v>
       </c>
@@ -23291,7 +23341,7 @@
       <c r="R318" s="11"/>
       <c r="S318" s="16"/>
     </row>
-    <row r="319" spans="1:19">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>318</v>
       </c>
@@ -23314,7 +23364,7 @@
       <c r="R319" s="11"/>
       <c r="S319" s="16"/>
     </row>
-    <row r="320" spans="1:19">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>319</v>
       </c>
@@ -23337,7 +23387,7 @@
       <c r="R320" s="11"/>
       <c r="S320" s="16"/>
     </row>
-    <row r="321" spans="1:19">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>320</v>
       </c>
@@ -23360,7 +23410,7 @@
       <c r="R321" s="11"/>
       <c r="S321" s="16"/>
     </row>
-    <row r="322" spans="1:19">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>321</v>
       </c>
@@ -23383,7 +23433,7 @@
       <c r="R322" s="11"/>
       <c r="S322" s="16"/>
     </row>
-    <row r="323" spans="1:19">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>322</v>
       </c>
@@ -23406,7 +23456,7 @@
       <c r="R323" s="11"/>
       <c r="S323" s="16"/>
     </row>
-    <row r="324" spans="1:19">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>323</v>
       </c>
@@ -23429,7 +23479,7 @@
       <c r="R324" s="11"/>
       <c r="S324" s="16"/>
     </row>
-    <row r="325" spans="1:19">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>324</v>
       </c>
@@ -23452,7 +23502,7 @@
       <c r="R325" s="11"/>
       <c r="S325" s="16"/>
     </row>
-    <row r="326" spans="1:19">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>325</v>
       </c>
@@ -23475,7 +23525,7 @@
       <c r="R326" s="11"/>
       <c r="S326" s="16"/>
     </row>
-    <row r="327" spans="1:19">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>326</v>
       </c>
@@ -23498,7 +23548,7 @@
       <c r="R327" s="11"/>
       <c r="S327" s="16"/>
     </row>
-    <row r="328" spans="1:19">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>327</v>
       </c>
@@ -23521,7 +23571,7 @@
       <c r="R328" s="11"/>
       <c r="S328" s="16"/>
     </row>
-    <row r="329" spans="1:19">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>328</v>
       </c>
@@ -23544,7 +23594,7 @@
       <c r="R329" s="11"/>
       <c r="S329" s="16"/>
     </row>
-    <row r="330" spans="1:19">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>329</v>
       </c>
@@ -23567,7 +23617,7 @@
       <c r="R330" s="11"/>
       <c r="S330" s="16"/>
     </row>
-    <row r="331" spans="1:19">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>330</v>
       </c>
@@ -23590,7 +23640,7 @@
       <c r="R331" s="11"/>
       <c r="S331" s="16"/>
     </row>
-    <row r="332" spans="1:19">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>331</v>
       </c>
@@ -23613,7 +23663,7 @@
       <c r="R332" s="11"/>
       <c r="S332" s="16"/>
     </row>
-    <row r="333" spans="1:19">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>332</v>
       </c>
@@ -23636,7 +23686,7 @@
       <c r="R333" s="11"/>
       <c r="S333" s="16"/>
     </row>
-    <row r="334" spans="1:19">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>333</v>
       </c>
@@ -23659,7 +23709,7 @@
       <c r="R334" s="11"/>
       <c r="S334" s="16"/>
     </row>
-    <row r="335" spans="1:19">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>334</v>
       </c>
@@ -23682,7 +23732,7 @@
       <c r="R335" s="11"/>
       <c r="S335" s="16"/>
     </row>
-    <row r="336" spans="1:19">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>335</v>
       </c>
@@ -23705,7 +23755,7 @@
       <c r="R336" s="11"/>
       <c r="S336" s="16"/>
     </row>
-    <row r="337" spans="1:19">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>336</v>
       </c>
@@ -23728,7 +23778,7 @@
       <c r="R337" s="11"/>
       <c r="S337" s="16"/>
     </row>
-    <row r="338" spans="1:19">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>337</v>
       </c>
@@ -23751,7 +23801,7 @@
       <c r="R338" s="11"/>
       <c r="S338" s="16"/>
     </row>
-    <row r="339" spans="1:19">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>338</v>
       </c>
@@ -23774,7 +23824,7 @@
       <c r="R339" s="11"/>
       <c r="S339" s="16"/>
     </row>
-    <row r="340" spans="1:19">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>339</v>
       </c>
@@ -23797,7 +23847,7 @@
       <c r="R340" s="11"/>
       <c r="S340" s="16"/>
     </row>
-    <row r="341" spans="1:19">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>340</v>
       </c>
@@ -23820,7 +23870,7 @@
       <c r="R341" s="11"/>
       <c r="S341" s="16"/>
     </row>
-    <row r="342" spans="1:19">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>341</v>
       </c>
@@ -23843,7 +23893,7 @@
       <c r="R342" s="11"/>
       <c r="S342" s="16"/>
     </row>
-    <row r="343" spans="1:19">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>342</v>
       </c>
@@ -23866,7 +23916,7 @@
       <c r="R343" s="11"/>
       <c r="S343" s="16"/>
     </row>
-    <row r="344" spans="1:19">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>343</v>
       </c>
@@ -23889,7 +23939,7 @@
       <c r="R344" s="11"/>
       <c r="S344" s="16"/>
     </row>
-    <row r="345" spans="1:19">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>344</v>
       </c>
@@ -23912,7 +23962,7 @@
       <c r="R345" s="11"/>
       <c r="S345" s="16"/>
     </row>
-    <row r="346" spans="1:19">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>345</v>
       </c>
@@ -23935,7 +23985,7 @@
       <c r="R346" s="11"/>
       <c r="S346" s="16"/>
     </row>
-    <row r="347" spans="1:19">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>346</v>
       </c>
@@ -23958,7 +24008,7 @@
       <c r="R347" s="11"/>
       <c r="S347" s="16"/>
     </row>
-    <row r="348" spans="1:19">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>347</v>
       </c>
@@ -23981,7 +24031,7 @@
       <c r="R348" s="11"/>
       <c r="S348" s="16"/>
     </row>
-    <row r="349" spans="1:19">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>348</v>
       </c>
@@ -24004,7 +24054,7 @@
       <c r="R349" s="11"/>
       <c r="S349" s="16"/>
     </row>
-    <row r="350" spans="1:19">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>349</v>
       </c>
@@ -24027,7 +24077,7 @@
       <c r="R350" s="11"/>
       <c r="S350" s="16"/>
     </row>
-    <row r="351" spans="1:19">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>350</v>
       </c>
@@ -24050,7 +24100,7 @@
       <c r="R351" s="11"/>
       <c r="S351" s="16"/>
     </row>
-    <row r="352" spans="1:19">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>351</v>
       </c>
@@ -24073,7 +24123,7 @@
       <c r="R352" s="11"/>
       <c r="S352" s="16"/>
     </row>
-    <row r="353" spans="1:19">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>352</v>
       </c>
@@ -24096,7 +24146,7 @@
       <c r="R353" s="11"/>
       <c r="S353" s="16"/>
     </row>
-    <row r="354" spans="1:19">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>353</v>
       </c>
@@ -24119,7 +24169,7 @@
       <c r="R354" s="11"/>
       <c r="S354" s="16"/>
     </row>
-    <row r="355" spans="1:19">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>354</v>
       </c>
@@ -24142,7 +24192,7 @@
       <c r="R355" s="11"/>
       <c r="S355" s="16"/>
     </row>
-    <row r="356" spans="1:19">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>355</v>
       </c>
@@ -24165,7 +24215,7 @@
       <c r="R356" s="11"/>
       <c r="S356" s="16"/>
     </row>
-    <row r="357" spans="1:19">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>356</v>
       </c>
@@ -24188,7 +24238,7 @@
       <c r="R357" s="11"/>
       <c r="S357" s="16"/>
     </row>
-    <row r="358" spans="1:19">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>357</v>
       </c>
@@ -24211,7 +24261,7 @@
       <c r="R358" s="11"/>
       <c r="S358" s="16"/>
     </row>
-    <row r="359" spans="1:19">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>358</v>
       </c>
@@ -24234,7 +24284,7 @@
       <c r="R359" s="11"/>
       <c r="S359" s="16"/>
     </row>
-    <row r="360" spans="1:19">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>359</v>
       </c>
@@ -24257,7 +24307,7 @@
       <c r="R360" s="11"/>
       <c r="S360" s="16"/>
     </row>
-    <row r="361" spans="1:19">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>360</v>
       </c>
@@ -24280,7 +24330,7 @@
       <c r="R361" s="11"/>
       <c r="S361" s="16"/>
     </row>
-    <row r="362" spans="1:19">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>361</v>
       </c>
@@ -24303,7 +24353,7 @@
       <c r="R362" s="11"/>
       <c r="S362" s="16"/>
     </row>
-    <row r="363" spans="1:19">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>362</v>
       </c>
@@ -24326,7 +24376,7 @@
       <c r="R363" s="11"/>
       <c r="S363" s="16"/>
     </row>
-    <row r="364" spans="1:19">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>363</v>
       </c>
@@ -24349,7 +24399,7 @@
       <c r="R364" s="11"/>
       <c r="S364" s="16"/>
     </row>
-    <row r="365" spans="1:19">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <v>364</v>
       </c>
@@ -24372,7 +24422,7 @@
       <c r="R365" s="11"/>
       <c r="S365" s="16"/>
     </row>
-    <row r="366" spans="1:19">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>365</v>
       </c>
@@ -24395,7 +24445,7 @@
       <c r="R366" s="11"/>
       <c r="S366" s="16"/>
     </row>
-    <row r="367" spans="1:19">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <v>366</v>
       </c>
@@ -24418,7 +24468,7 @@
       <c r="R367" s="11"/>
       <c r="S367" s="16"/>
     </row>
-    <row r="368" spans="1:19">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>367</v>
       </c>
@@ -24441,7 +24491,7 @@
       <c r="R368" s="11"/>
       <c r="S368" s="16"/>
     </row>
-    <row r="369" spans="1:19">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <v>368</v>
       </c>
@@ -24464,7 +24514,7 @@
       <c r="R369" s="11"/>
       <c r="S369" s="16"/>
     </row>
-    <row r="370" spans="1:19">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <v>369</v>
       </c>
@@ -24487,7 +24537,7 @@
       <c r="R370" s="11"/>
       <c r="S370" s="16"/>
     </row>
-    <row r="371" spans="1:19">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <v>370</v>
       </c>
@@ -24510,7 +24560,7 @@
       <c r="R371" s="11"/>
       <c r="S371" s="16"/>
     </row>
-    <row r="372" spans="1:19">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A372" s="2">
         <v>371</v>
       </c>
@@ -24533,7 +24583,7 @@
       <c r="R372" s="11"/>
       <c r="S372" s="16"/>
     </row>
-    <row r="373" spans="1:19">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <v>372</v>
       </c>
@@ -24556,7 +24606,7 @@
       <c r="R373" s="11"/>
       <c r="S373" s="16"/>
     </row>
-    <row r="374" spans="1:19">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <v>373</v>
       </c>
@@ -24579,7 +24629,7 @@
       <c r="R374" s="11"/>
       <c r="S374" s="16"/>
     </row>
-    <row r="375" spans="1:19">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A375" s="2">
         <v>374</v>
       </c>
@@ -24602,7 +24652,7 @@
       <c r="R375" s="11"/>
       <c r="S375" s="16"/>
     </row>
-    <row r="376" spans="1:19">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <v>375</v>
       </c>
@@ -24625,7 +24675,7 @@
       <c r="R376" s="11"/>
       <c r="S376" s="16"/>
     </row>
-    <row r="377" spans="1:19">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A377" s="2">
         <v>376</v>
       </c>
@@ -24648,7 +24698,7 @@
       <c r="R377" s="11"/>
       <c r="S377" s="16"/>
     </row>
-    <row r="378" spans="1:19">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A378" s="2">
         <v>377</v>
       </c>
@@ -24671,7 +24721,7 @@
       <c r="R378" s="11"/>
       <c r="S378" s="16"/>
     </row>
-    <row r="379" spans="1:19">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A379" s="2">
         <v>378</v>
       </c>
@@ -24694,7 +24744,7 @@
       <c r="R379" s="11"/>
       <c r="S379" s="16"/>
     </row>
-    <row r="380" spans="1:19">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A380" s="2">
         <v>379</v>
       </c>
@@ -24717,7 +24767,7 @@
       <c r="R380" s="11"/>
       <c r="S380" s="16"/>
     </row>
-    <row r="381" spans="1:19">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A381" s="2">
         <v>380</v>
       </c>
@@ -24740,7 +24790,7 @@
       <c r="R381" s="11"/>
       <c r="S381" s="16"/>
     </row>
-    <row r="382" spans="1:19">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A382" s="2">
         <v>381</v>
       </c>
@@ -24763,7 +24813,7 @@
       <c r="R382" s="11"/>
       <c r="S382" s="16"/>
     </row>
-    <row r="383" spans="1:19">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A383" s="2">
         <v>382</v>
       </c>
@@ -24786,7 +24836,7 @@
       <c r="R383" s="11"/>
       <c r="S383" s="16"/>
     </row>
-    <row r="384" spans="1:19">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A384" s="2">
         <v>383</v>
       </c>
@@ -24809,7 +24859,7 @@
       <c r="R384" s="11"/>
       <c r="S384" s="16"/>
     </row>
-    <row r="385" spans="1:19">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A385" s="2">
         <v>384</v>
       </c>
@@ -24832,7 +24882,7 @@
       <c r="R385" s="11"/>
       <c r="S385" s="16"/>
     </row>
-    <row r="386" spans="1:19">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A386" s="2">
         <v>385</v>
       </c>
@@ -24855,7 +24905,7 @@
       <c r="R386" s="11"/>
       <c r="S386" s="16"/>
     </row>
-    <row r="387" spans="1:19">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A387" s="2">
         <v>386</v>
       </c>
@@ -24878,7 +24928,7 @@
       <c r="R387" s="11"/>
       <c r="S387" s="16"/>
     </row>
-    <row r="388" spans="1:19">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A388" s="2">
         <v>387</v>
       </c>
@@ -24901,7 +24951,7 @@
       <c r="R388" s="11"/>
       <c r="S388" s="16"/>
     </row>
-    <row r="389" spans="1:19">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A389" s="2">
         <v>388</v>
       </c>
@@ -24924,7 +24974,7 @@
       <c r="R389" s="11"/>
       <c r="S389" s="16"/>
     </row>
-    <row r="390" spans="1:19">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A390" s="2">
         <v>389</v>
       </c>
@@ -24947,7 +24997,7 @@
       <c r="R390" s="11"/>
       <c r="S390" s="16"/>
     </row>
-    <row r="391" spans="1:19">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A391" s="2">
         <v>390</v>
       </c>
@@ -24970,7 +25020,7 @@
       <c r="R391" s="11"/>
       <c r="S391" s="16"/>
     </row>
-    <row r="392" spans="1:19">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A392" s="2">
         <v>391</v>
       </c>
@@ -24993,7 +25043,7 @@
       <c r="R392" s="11"/>
       <c r="S392" s="16"/>
     </row>
-    <row r="393" spans="1:19">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A393" s="2">
         <v>392</v>
       </c>
@@ -25016,7 +25066,7 @@
       <c r="R393" s="11"/>
       <c r="S393" s="16"/>
     </row>
-    <row r="394" spans="1:19">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A394" s="2">
         <v>393</v>
       </c>
@@ -25039,7 +25089,7 @@
       <c r="R394" s="11"/>
       <c r="S394" s="16"/>
     </row>
-    <row r="395" spans="1:19">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A395" s="2">
         <v>394</v>
       </c>
@@ -25062,7 +25112,7 @@
       <c r="R395" s="11"/>
       <c r="S395" s="16"/>
     </row>
-    <row r="396" spans="1:19">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A396" s="2">
         <v>395</v>
       </c>
@@ -25085,7 +25135,7 @@
       <c r="R396" s="11"/>
       <c r="S396" s="16"/>
     </row>
-    <row r="397" spans="1:19">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A397" s="2">
         <v>396</v>
       </c>
@@ -25108,7 +25158,7 @@
       <c r="R397" s="11"/>
       <c r="S397" s="16"/>
     </row>
-    <row r="398" spans="1:19">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A398" s="2">
         <v>397</v>
       </c>
@@ -25131,7 +25181,7 @@
       <c r="R398" s="11"/>
       <c r="S398" s="16"/>
     </row>
-    <row r="399" spans="1:19">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A399" s="2">
         <v>398</v>
       </c>
@@ -25154,7 +25204,7 @@
       <c r="R399" s="11"/>
       <c r="S399" s="16"/>
     </row>
-    <row r="400" spans="1:19">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A400" s="2">
         <v>399</v>
       </c>
@@ -25177,7 +25227,7 @@
       <c r="R400" s="11"/>
       <c r="S400" s="16"/>
     </row>
-    <row r="401" spans="1:19">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A401" s="2">
         <v>400</v>
       </c>
@@ -25200,7 +25250,7 @@
       <c r="R401" s="11"/>
       <c r="S401" s="16"/>
     </row>
-    <row r="402" spans="1:19">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A402" s="2">
         <v>401</v>
       </c>
@@ -25223,7 +25273,7 @@
       <c r="R402" s="11"/>
       <c r="S402" s="16"/>
     </row>
-    <row r="403" spans="1:19">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A403" s="2">
         <v>402</v>
       </c>
@@ -25246,7 +25296,7 @@
       <c r="R403" s="11"/>
       <c r="S403" s="16"/>
     </row>
-    <row r="404" spans="1:19">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A404" s="2">
         <v>403</v>
       </c>
@@ -25269,7 +25319,7 @@
       <c r="R404" s="11"/>
       <c r="S404" s="16"/>
     </row>
-    <row r="405" spans="1:19">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A405" s="2">
         <v>404</v>
       </c>
@@ -25292,7 +25342,7 @@
       <c r="R405" s="11"/>
       <c r="S405" s="16"/>
     </row>
-    <row r="406" spans="1:19">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A406" s="2">
         <v>405</v>
       </c>
@@ -25315,7 +25365,7 @@
       <c r="R406" s="11"/>
       <c r="S406" s="16"/>
     </row>
-    <row r="407" spans="1:19">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A407" s="2">
         <v>406</v>
       </c>
@@ -25338,7 +25388,7 @@
       <c r="R407" s="11"/>
       <c r="S407" s="16"/>
     </row>
-    <row r="408" spans="1:19">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A408" s="2">
         <v>407</v>
       </c>
@@ -25361,7 +25411,7 @@
       <c r="R408" s="11"/>
       <c r="S408" s="16"/>
     </row>
-    <row r="409" spans="1:19">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A409" s="2">
         <v>408</v>
       </c>
@@ -25384,7 +25434,7 @@
       <c r="R409" s="11"/>
       <c r="S409" s="16"/>
     </row>
-    <row r="410" spans="1:19">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A410" s="2">
         <v>409</v>
       </c>
@@ -25407,7 +25457,7 @@
       <c r="R410" s="11"/>
       <c r="S410" s="16"/>
     </row>
-    <row r="411" spans="1:19">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A411" s="2">
         <v>410</v>
       </c>
@@ -25430,7 +25480,7 @@
       <c r="R411" s="11"/>
       <c r="S411" s="16"/>
     </row>
-    <row r="412" spans="1:19">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A412" s="2">
         <v>411</v>
       </c>
@@ -25453,7 +25503,7 @@
       <c r="R412" s="11"/>
       <c r="S412" s="16"/>
     </row>
-    <row r="413" spans="1:19">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A413" s="2">
         <v>412</v>
       </c>
@@ -25476,7 +25526,7 @@
       <c r="R413" s="11"/>
       <c r="S413" s="16"/>
     </row>
-    <row r="414" spans="1:19">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A414" s="2">
         <v>413</v>
       </c>
@@ -25499,7 +25549,7 @@
       <c r="R414" s="11"/>
       <c r="S414" s="16"/>
     </row>
-    <row r="415" spans="1:19">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A415" s="2">
         <v>414</v>
       </c>
@@ -25522,7 +25572,7 @@
       <c r="R415" s="11"/>
       <c r="S415" s="16"/>
     </row>
-    <row r="416" spans="1:19">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A416" s="2">
         <v>415</v>
       </c>
@@ -25545,7 +25595,7 @@
       <c r="R416" s="11"/>
       <c r="S416" s="16"/>
     </row>
-    <row r="417" spans="1:19">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A417" s="2">
         <v>416</v>
       </c>
@@ -25568,7 +25618,7 @@
       <c r="R417" s="11"/>
       <c r="S417" s="16"/>
     </row>
-    <row r="418" spans="1:19">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A418" s="2">
         <v>417</v>
       </c>
@@ -25591,7 +25641,7 @@
       <c r="R418" s="11"/>
       <c r="S418" s="16"/>
     </row>
-    <row r="419" spans="1:19">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A419" s="2">
         <v>418</v>
       </c>
@@ -25614,7 +25664,7 @@
       <c r="R419" s="11"/>
       <c r="S419" s="16"/>
     </row>
-    <row r="420" spans="1:19">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A420" s="2">
         <v>419</v>
       </c>
@@ -25637,7 +25687,7 @@
       <c r="R420" s="11"/>
       <c r="S420" s="16"/>
     </row>
-    <row r="421" spans="1:19">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A421" s="2">
         <v>420</v>
       </c>
@@ -25660,7 +25710,7 @@
       <c r="R421" s="11"/>
       <c r="S421" s="16"/>
     </row>
-    <row r="422" spans="1:19">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A422" s="2">
         <v>421</v>
       </c>
@@ -25683,7 +25733,7 @@
       <c r="R422" s="11"/>
       <c r="S422" s="16"/>
     </row>
-    <row r="423" spans="1:19">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A423" s="2">
         <v>422</v>
       </c>
@@ -25706,7 +25756,7 @@
       <c r="R423" s="11"/>
       <c r="S423" s="16"/>
     </row>
-    <row r="424" spans="1:19">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A424" s="2">
         <v>423</v>
       </c>
@@ -25729,7 +25779,7 @@
       <c r="R424" s="11"/>
       <c r="S424" s="16"/>
     </row>
-    <row r="425" spans="1:19">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A425" s="2">
         <v>424</v>
       </c>
@@ -25752,7 +25802,7 @@
       <c r="R425" s="11"/>
       <c r="S425" s="16"/>
     </row>
-    <row r="426" spans="1:19">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A426" s="2">
         <v>425</v>
       </c>
@@ -25775,7 +25825,7 @@
       <c r="R426" s="11"/>
       <c r="S426" s="16"/>
     </row>
-    <row r="427" spans="1:19">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A427" s="2">
         <v>426</v>
       </c>
@@ -25798,7 +25848,7 @@
       <c r="R427" s="11"/>
       <c r="S427" s="16"/>
     </row>
-    <row r="428" spans="1:19">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A428" s="2">
         <v>427</v>
       </c>
@@ -25821,7 +25871,7 @@
       <c r="R428" s="11"/>
       <c r="S428" s="16"/>
     </row>
-    <row r="429" spans="1:19">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A429" s="2">
         <v>428</v>
       </c>
@@ -25844,7 +25894,7 @@
       <c r="R429" s="11"/>
       <c r="S429" s="16"/>
     </row>
-    <row r="430" spans="1:19">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A430" s="2">
         <v>429</v>
       </c>
@@ -25867,7 +25917,7 @@
       <c r="R430" s="11"/>
       <c r="S430" s="16"/>
     </row>
-    <row r="431" spans="1:19">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A431" s="2">
         <v>430</v>
       </c>
@@ -25890,7 +25940,7 @@
       <c r="R431" s="11"/>
       <c r="S431" s="16"/>
     </row>
-    <row r="432" spans="1:19">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A432" s="2">
         <v>431</v>
       </c>
@@ -25913,7 +25963,7 @@
       <c r="R432" s="11"/>
       <c r="S432" s="16"/>
     </row>
-    <row r="433" spans="1:19">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A433" s="2">
         <v>432</v>
       </c>
@@ -25936,7 +25986,7 @@
       <c r="R433" s="11"/>
       <c r="S433" s="16"/>
     </row>
-    <row r="434" spans="1:19">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A434" s="2">
         <v>433</v>
       </c>
@@ -25959,7 +26009,7 @@
       <c r="R434" s="11"/>
       <c r="S434" s="16"/>
     </row>
-    <row r="435" spans="1:19">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A435" s="2">
         <v>434</v>
       </c>
@@ -25982,7 +26032,7 @@
       <c r="R435" s="11"/>
       <c r="S435" s="16"/>
     </row>
-    <row r="436" spans="1:19">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A436" s="2">
         <v>435</v>
       </c>
@@ -26005,7 +26055,7 @@
       <c r="R436" s="11"/>
       <c r="S436" s="16"/>
     </row>
-    <row r="437" spans="1:19">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A437" s="2">
         <v>436</v>
       </c>
@@ -26028,7 +26078,7 @@
       <c r="R437" s="11"/>
       <c r="S437" s="16"/>
     </row>
-    <row r="438" spans="1:19">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A438" s="2">
         <v>437</v>
       </c>
@@ -26051,7 +26101,7 @@
       <c r="R438" s="11"/>
       <c r="S438" s="16"/>
     </row>
-    <row r="439" spans="1:19">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A439" s="2">
         <v>438</v>
       </c>
@@ -26074,7 +26124,7 @@
       <c r="R439" s="11"/>
       <c r="S439" s="16"/>
     </row>
-    <row r="440" spans="1:19">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A440" s="2">
         <v>439</v>
       </c>
@@ -26097,7 +26147,7 @@
       <c r="R440" s="11"/>
       <c r="S440" s="16"/>
     </row>
-    <row r="441" spans="1:19">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A441" s="2">
         <v>440</v>
       </c>
@@ -26120,7 +26170,7 @@
       <c r="R441" s="11"/>
       <c r="S441" s="16"/>
     </row>
-    <row r="442" spans="1:19">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A442" s="2">
         <v>441</v>
       </c>
@@ -26143,7 +26193,7 @@
       <c r="R442" s="11"/>
       <c r="S442" s="16"/>
     </row>
-    <row r="443" spans="1:19">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A443" s="2">
         <v>442</v>
       </c>
@@ -26166,7 +26216,7 @@
       <c r="R443" s="11"/>
       <c r="S443" s="16"/>
     </row>
-    <row r="444" spans="1:19">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A444" s="2">
         <v>443</v>
       </c>
@@ -26189,7 +26239,7 @@
       <c r="R444" s="11"/>
       <c r="S444" s="16"/>
     </row>
-    <row r="445" spans="1:19">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A445" s="2">
         <v>444</v>
       </c>
@@ -26212,7 +26262,7 @@
       <c r="R445" s="11"/>
       <c r="S445" s="16"/>
     </row>
-    <row r="446" spans="1:19">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A446" s="2">
         <v>445</v>
       </c>
@@ -26235,7 +26285,7 @@
       <c r="R446" s="11"/>
       <c r="S446" s="16"/>
     </row>
-    <row r="447" spans="1:19">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A447" s="2">
         <v>446</v>
       </c>
@@ -26258,7 +26308,7 @@
       <c r="R447" s="11"/>
       <c r="S447" s="16"/>
     </row>
-    <row r="448" spans="1:19">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A448" s="2">
         <v>447</v>
       </c>
@@ -26281,7 +26331,7 @@
       <c r="R448" s="11"/>
       <c r="S448" s="16"/>
     </row>
-    <row r="449" spans="1:19">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A449" s="2">
         <v>448</v>
       </c>
@@ -26304,7 +26354,7 @@
       <c r="R449" s="11"/>
       <c r="S449" s="16"/>
     </row>
-    <row r="450" spans="1:19">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A450" s="2">
         <v>449</v>
       </c>
@@ -26327,7 +26377,7 @@
       <c r="R450" s="11"/>
       <c r="S450" s="16"/>
     </row>
-    <row r="451" spans="1:19">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A451" s="2">
         <v>450</v>
       </c>
@@ -26350,7 +26400,7 @@
       <c r="R451" s="11"/>
       <c r="S451" s="16"/>
     </row>
-    <row r="452" spans="1:19">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A452" s="2">
         <v>451</v>
       </c>
@@ -26373,7 +26423,7 @@
       <c r="R452" s="11"/>
       <c r="S452" s="16"/>
     </row>
-    <row r="453" spans="1:19">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A453" s="2">
         <v>452</v>
       </c>
@@ -26396,7 +26446,7 @@
       <c r="R453" s="11"/>
       <c r="S453" s="16"/>
     </row>
-    <row r="454" spans="1:19">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A454" s="2">
         <v>453</v>
       </c>
@@ -26419,7 +26469,7 @@
       <c r="R454" s="11"/>
       <c r="S454" s="16"/>
     </row>
-    <row r="455" spans="1:19">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A455" s="2">
         <v>454</v>
       </c>
@@ -26442,7 +26492,7 @@
       <c r="R455" s="11"/>
       <c r="S455" s="16"/>
     </row>
-    <row r="456" spans="1:19">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A456" s="2">
         <v>455</v>
       </c>
@@ -26465,7 +26515,7 @@
       <c r="R456" s="11"/>
       <c r="S456" s="16"/>
     </row>
-    <row r="457" spans="1:19">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A457" s="2">
         <v>456</v>
       </c>
@@ -26488,7 +26538,7 @@
       <c r="R457" s="11"/>
       <c r="S457" s="16"/>
     </row>
-    <row r="458" spans="1:19">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A458" s="2">
         <v>457</v>
       </c>
@@ -26511,7 +26561,7 @@
       <c r="R458" s="11"/>
       <c r="S458" s="16"/>
     </row>
-    <row r="459" spans="1:19">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A459" s="2">
         <v>458</v>
       </c>
@@ -26534,7 +26584,7 @@
       <c r="R459" s="11"/>
       <c r="S459" s="16"/>
     </row>
-    <row r="460" spans="1:19">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A460" s="2">
         <v>459</v>
       </c>
@@ -26557,7 +26607,7 @@
       <c r="R460" s="11"/>
       <c r="S460" s="16"/>
     </row>
-    <row r="461" spans="1:19">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A461" s="2">
         <v>460</v>
       </c>
@@ -26580,7 +26630,7 @@
       <c r="R461" s="11"/>
       <c r="S461" s="16"/>
     </row>
-    <row r="462" spans="1:19">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A462" s="2">
         <v>461</v>
       </c>
@@ -26603,7 +26653,7 @@
       <c r="R462" s="11"/>
       <c r="S462" s="16"/>
     </row>
-    <row r="463" spans="1:19">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A463" s="2">
         <v>462</v>
       </c>
@@ -26626,7 +26676,7 @@
       <c r="R463" s="11"/>
       <c r="S463" s="16"/>
     </row>
-    <row r="464" spans="1:19">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A464" s="2">
         <v>463</v>
       </c>
@@ -26649,7 +26699,7 @@
       <c r="R464" s="11"/>
       <c r="S464" s="16"/>
     </row>
-    <row r="465" spans="1:19">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A465" s="2">
         <v>464</v>
       </c>
@@ -26672,7 +26722,7 @@
       <c r="R465" s="11"/>
       <c r="S465" s="16"/>
     </row>
-    <row r="466" spans="1:19">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A466" s="2">
         <v>465</v>
       </c>
@@ -26695,7 +26745,7 @@
       <c r="R466" s="11"/>
       <c r="S466" s="16"/>
     </row>
-    <row r="467" spans="1:19">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A467" s="2">
         <v>466</v>
       </c>
@@ -26718,7 +26768,7 @@
       <c r="R467" s="11"/>
       <c r="S467" s="16"/>
     </row>
-    <row r="468" spans="1:19">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A468" s="2">
         <v>467</v>
       </c>
@@ -26741,7 +26791,7 @@
       <c r="R468" s="11"/>
       <c r="S468" s="16"/>
     </row>
-    <row r="469" spans="1:19">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A469" s="2">
         <v>468</v>
       </c>
@@ -26764,7 +26814,7 @@
       <c r="R469" s="11"/>
       <c r="S469" s="16"/>
     </row>
-    <row r="470" spans="1:19">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A470" s="2">
         <v>469</v>
       </c>
@@ -26787,7 +26837,7 @@
       <c r="R470" s="11"/>
       <c r="S470" s="16"/>
     </row>
-    <row r="471" spans="1:19">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A471" s="2">
         <v>470</v>
       </c>
@@ -26810,7 +26860,7 @@
       <c r="R471" s="11"/>
       <c r="S471" s="16"/>
     </row>
-    <row r="472" spans="1:19">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A472" s="2">
         <v>471</v>
       </c>
@@ -26833,7 +26883,7 @@
       <c r="R472" s="11"/>
       <c r="S472" s="16"/>
     </row>
-    <row r="473" spans="1:19">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A473" s="2">
         <v>472</v>
       </c>
@@ -26856,7 +26906,7 @@
       <c r="R473" s="11"/>
       <c r="S473" s="16"/>
     </row>
-    <row r="474" spans="1:19">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A474" s="2">
         <v>473</v>
       </c>
@@ -26879,7 +26929,7 @@
       <c r="R474" s="11"/>
       <c r="S474" s="16"/>
     </row>
-    <row r="475" spans="1:19">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A475" s="2">
         <v>474</v>
       </c>
@@ -26902,7 +26952,7 @@
       <c r="R475" s="11"/>
       <c r="S475" s="16"/>
     </row>
-    <row r="476" spans="1:19">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A476" s="2">
         <v>475</v>
       </c>
@@ -26925,7 +26975,7 @@
       <c r="R476" s="11"/>
       <c r="S476" s="16"/>
     </row>
-    <row r="477" spans="1:19">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A477" s="2">
         <v>476</v>
       </c>
@@ -26948,7 +26998,7 @@
       <c r="R477" s="11"/>
       <c r="S477" s="16"/>
     </row>
-    <row r="478" spans="1:19">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A478" s="2">
         <v>477</v>
       </c>
@@ -26971,7 +27021,7 @@
       <c r="R478" s="11"/>
       <c r="S478" s="16"/>
     </row>
-    <row r="479" spans="1:19">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A479" s="2">
         <v>478</v>
       </c>
@@ -26994,7 +27044,7 @@
       <c r="R479" s="11"/>
       <c r="S479" s="16"/>
     </row>
-    <row r="480" spans="1:19">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A480" s="2">
         <v>479</v>
       </c>
@@ -27017,7 +27067,7 @@
       <c r="R480" s="11"/>
       <c r="S480" s="16"/>
     </row>
-    <row r="481" spans="1:19">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A481" s="2">
         <v>480</v>
       </c>
@@ -27040,7 +27090,7 @@
       <c r="R481" s="11"/>
       <c r="S481" s="16"/>
     </row>
-    <row r="482" spans="1:19">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A482" s="2">
         <v>481</v>
       </c>
@@ -27063,7 +27113,7 @@
       <c r="R482" s="11"/>
       <c r="S482" s="16"/>
     </row>
-    <row r="483" spans="1:19">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A483" s="2">
         <v>482</v>
       </c>
@@ -27086,7 +27136,7 @@
       <c r="R483" s="11"/>
       <c r="S483" s="16"/>
     </row>
-    <row r="484" spans="1:19">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A484" s="2">
         <v>483</v>
       </c>
@@ -27109,7 +27159,7 @@
       <c r="R484" s="11"/>
       <c r="S484" s="16"/>
     </row>
-    <row r="485" spans="1:19">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A485" s="2">
         <v>484</v>
       </c>
@@ -27132,7 +27182,7 @@
       <c r="R485" s="11"/>
       <c r="S485" s="16"/>
     </row>
-    <row r="486" spans="1:19">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A486" s="2">
         <v>485</v>
       </c>
@@ -27155,7 +27205,7 @@
       <c r="R486" s="11"/>
       <c r="S486" s="16"/>
     </row>
-    <row r="487" spans="1:19">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A487" s="2">
         <v>486</v>
       </c>
@@ -27178,7 +27228,7 @@
       <c r="R487" s="11"/>
       <c r="S487" s="16"/>
     </row>
-    <row r="488" spans="1:19">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A488" s="2">
         <v>487</v>
       </c>
@@ -27201,7 +27251,7 @@
       <c r="R488" s="11"/>
       <c r="S488" s="16"/>
     </row>
-    <row r="489" spans="1:19">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A489" s="2">
         <v>488</v>
       </c>
@@ -27224,7 +27274,7 @@
       <c r="R489" s="11"/>
       <c r="S489" s="16"/>
     </row>
-    <row r="490" spans="1:19">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A490" s="2">
         <v>489</v>
       </c>
@@ -27247,7 +27297,7 @@
       <c r="R490" s="11"/>
       <c r="S490" s="16"/>
     </row>
-    <row r="491" spans="1:19">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A491" s="2">
         <v>490</v>
       </c>
@@ -27270,7 +27320,7 @@
       <c r="R491" s="11"/>
       <c r="S491" s="16"/>
     </row>
-    <row r="492" spans="1:19">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A492" s="2">
         <v>491</v>
       </c>
@@ -27293,7 +27343,7 @@
       <c r="R492" s="11"/>
       <c r="S492" s="16"/>
     </row>
-    <row r="493" spans="1:19">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A493" s="2">
         <v>492</v>
       </c>
@@ -27316,7 +27366,7 @@
       <c r="R493" s="11"/>
       <c r="S493" s="16"/>
     </row>
-    <row r="494" spans="1:19">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A494" s="2">
         <v>493</v>
       </c>
@@ -27339,7 +27389,7 @@
       <c r="R494" s="11"/>
       <c r="S494" s="16"/>
     </row>
-    <row r="495" spans="1:19">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A495" s="2">
         <v>494</v>
       </c>
@@ -27362,7 +27412,7 @@
       <c r="R495" s="11"/>
       <c r="S495" s="16"/>
     </row>
-    <row r="496" spans="1:19">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A496" s="2">
         <v>495</v>
       </c>
@@ -27385,7 +27435,7 @@
       <c r="R496" s="11"/>
       <c r="S496" s="16"/>
     </row>
-    <row r="497" spans="1:19">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A497" s="2">
         <v>496</v>
       </c>
@@ -27408,7 +27458,7 @@
       <c r="R497" s="11"/>
       <c r="S497" s="16"/>
     </row>
-    <row r="498" spans="1:19">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A498" s="2">
         <v>497</v>
       </c>
@@ -27431,7 +27481,7 @@
       <c r="R498" s="11"/>
       <c r="S498" s="16"/>
     </row>
-    <row r="499" spans="1:19">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A499" s="2">
         <v>498</v>
       </c>
@@ -27454,7 +27504,7 @@
       <c r="R499" s="11"/>
       <c r="S499" s="16"/>
     </row>
-    <row r="500" spans="1:19">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A500" s="2">
         <v>499</v>
       </c>
@@ -27477,7 +27527,7 @@
       <c r="R500" s="11"/>
       <c r="S500" s="16"/>
     </row>
-    <row r="501" spans="1:19">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B501" s="26" t="s">
         <v>41</v>
       </c>
@@ -27553,19 +27603,19 @@
           <x14:formula1>
             <xm:f>DADOS!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>Q52:R52 Q20:R21 P18:P500 Q26:R26</xm:sqref>
+          <xm:sqref>Q52:R52 Q20:R21 Q26:R26 P18:P500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9F7C393D-314F-4835-8933-4048B330493F}">
           <x14:formula1>
             <xm:f>DADOS!$F$2:$F$4</xm:f>
           </x14:formula1>
-          <xm:sqref>R24 Q53:Q500 R19 R27 Q18:Q19 Q22:Q25 Q27:Q51</xm:sqref>
+          <xm:sqref>R24 Q27:Q51 R19 R27 Q18:Q19 Q22:Q25 Q53:Q500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCE72C4-F5BB-44C1-9C17-2DA270136EBC}">
           <x14:formula1>
             <xm:f>DADOS!$G$2:$G$4</xm:f>
           </x14:formula1>
-          <xm:sqref>R53:R500 R22:R23 R28:R51 R18 R25</xm:sqref>
+          <xm:sqref>R25 R22:R23 R28:R51 R18 R53:R500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6301E476-8B0D-4FEC-83CC-54871B5A47EA}">
           <x14:formula1>
@@ -27592,15 +27642,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010071220A11FEA46C4886D3604CC483AD6B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="bb07fbe832bfbac930195f44faefcab7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2" xmlns:ns3="8de5c96d-c68a-4bc1-8ca7-a6766c74fd4d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71ce47b93599878504e7d9a94c5299da" ns2:_="" ns3:_="">
     <xsd:import namespace="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
@@ -27829,7 +27870,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
@@ -27839,14 +27880,48 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C5C945-474E-4133-9AF8-55A4124AD51D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+    <ds:schemaRef ds:uri="8de5c96d-c68a-4bc1-8ca7-a6766c74fd4d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C5C945-474E-4133-9AF8-55A4124AD51D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/9. PCM - Previsão de Gastos 2025 e 2026.xlsx
+++ b/9. PCM - Previsão de Gastos 2025 e 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\pcmauro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623D6F55-3CA4-41D7-8896-C57074F1BF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294425A8-FE3E-495A-9774-981DD215BC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
+    <workbookView xWindow="60" yWindow="135" windowWidth="28605" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="DADOS" sheetId="2" r:id="rId1"/>
@@ -17259,13 +17259,13 @@
       <c r="N54" s="13"/>
       <c r="O54" s="13"/>
       <c r="P54" s="11" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q54" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R54" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="S54" s="16"/>
     </row>
@@ -27642,6 +27642,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010071220A11FEA46C4886D3604CC483AD6B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="bb07fbe832bfbac930195f44faefcab7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2" xmlns:ns3="8de5c96d-c68a-4bc1-8ca7-a6766c74fd4d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71ce47b93599878504e7d9a94c5299da" ns2:_="" ns3:_="">
     <xsd:import namespace="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
@@ -27870,26 +27889,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C5C945-474E-4133-9AF8-55A4124AD51D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27906,22 +27924,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>